--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>122789</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>17.9599990844727</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>182983</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>18.2600002288818</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>17.5200004577637</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>17.8400001525879</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>17.9799995422363</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>107162</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>17.9799995422363</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>18.3199996948242</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>174699</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>97437</v>
+        <v>66569</v>
       </c>
       <c r="C2715" t="n">
-        <v>17.5</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="D2715" t="n">
-        <v>16.9599990844727</v>
+        <v>17</v>
       </c>
       <c r="E2715" t="n">
-        <v>17.1000003814697</v>
+        <v>17</v>
       </c>
       <c r="F2715" t="n">
-        <v>17.2999992370605</v>
+        <v>17.3199996948242</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>129168</v>
+        <v>97437</v>
       </c>
       <c r="C2716" t="n">
-        <v>17.6599998474121</v>
+        <v>17.5</v>
       </c>
       <c r="D2716" t="n">
-        <v>17.0799999237061</v>
+        <v>16.9599990844727</v>
       </c>
       <c r="E2716" t="n">
-        <v>17.1200008392334</v>
+        <v>17.1000003814697</v>
       </c>
       <c r="F2716" t="n">
-        <v>17.5</v>
+        <v>17.2999992370605</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>131979</v>
+        <v>129168</v>
       </c>
       <c r="C2717" t="n">
-        <v>17.8999996185303</v>
+        <v>17.6599998474121</v>
       </c>
       <c r="D2717" t="n">
-        <v>17.3999996185303</v>
+        <v>17.0799999237061</v>
       </c>
       <c r="E2717" t="n">
-        <v>17.7000007629395</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="F2717" t="n">
-        <v>17.4799995422363</v>
+        <v>17.5</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>69974</v>
+        <v>131979</v>
       </c>
       <c r="C2718" t="n">
-        <v>17.8199996948242</v>
+        <v>17.8999996185303</v>
       </c>
       <c r="D2718" t="n">
         <v>17.3999996185303</v>
       </c>
       <c r="E2718" t="n">
-        <v>17.3999996185303</v>
+        <v>17.7000007629395</v>
       </c>
       <c r="F2718" t="n">
-        <v>17.6399993896484</v>
+        <v>17.4799995422363</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>122789</v>
+        <v>69974</v>
       </c>
       <c r="C2719" t="n">
-        <v>17.9599990844727</v>
+        <v>17.8199996948242</v>
       </c>
       <c r="D2719" t="n">
-        <v>17.5</v>
+        <v>17.3999996185303</v>
       </c>
       <c r="E2719" t="n">
-        <v>17.7999992370605</v>
+        <v>17.3999996185303</v>
       </c>
       <c r="F2719" t="n">
-        <v>17.7000007629395</v>
+        <v>17.6399993896484</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>182983</v>
+        <v>122789</v>
       </c>
       <c r="C2720" t="n">
-        <v>18.2600002288818</v>
+        <v>17.9599990844727</v>
       </c>
       <c r="D2720" t="n">
-        <v>17.5200004577637</v>
+        <v>17.5</v>
       </c>
       <c r="E2720" t="n">
-        <v>17.8400001525879</v>
+        <v>17.7999992370605</v>
       </c>
       <c r="F2720" t="n">
-        <v>17.9799995422363</v>
+        <v>17.7000007629395</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>107162</v>
+        <v>182983</v>
       </c>
       <c r="C2721" t="n">
-        <v>18.3999996185303</v>
+        <v>18.2600002288818</v>
       </c>
       <c r="D2721" t="n">
+        <v>17.5200004577637</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>17.8400001525879</v>
+      </c>
+      <c r="F2721" t="n">
         <v>17.9799995422363</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>18.2000007629395</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>18.3199996948242</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>174699</v>
+        <v>107162</v>
       </c>
       <c r="C2722" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>17.9799995422363</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>18.3199996948242</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1323319</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>19.0200004577637</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>18.0799999237061</v>
+      </c>
+      <c r="E2723" t="n">
         <v>18.8999996185303</v>
       </c>
-      <c r="D2722" t="n">
-        <v>18</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>18.8400001525879</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>18.0799999237061</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73344707489014</v>
+        <v>1.73344719409943</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.70982086658478</v>
+        <v>1.70982015132904</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71106398105621</v>
+        <v>1.7110641002655</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71355092525482</v>
+        <v>1.71355080604553</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65634953975677</v>
+        <v>1.65634965896606</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57925224304199</v>
+        <v>1.57925236225128</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5854697227478</v>
+        <v>1.58547008037567</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G10" t="n">
-        <v>1.56557393074036</v>
+        <v>1.56557369232178</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52329432964325</v>
+        <v>1.52329468727112</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G12" t="n">
-        <v>1.42008376121521</v>
+        <v>1.42008352279663</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.55438232421875</v>
+        <v>1.55438196659088</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41759634017944</v>
+        <v>1.41759657859802</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46111929416656</v>
+        <v>1.46111917495728</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>1.53075551986694</v>
+        <v>1.53075540065765</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46236300468445</v>
+        <v>1.46236276626587</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45490157604218</v>
+        <v>1.45490181446075</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5083726644516</v>
+        <v>1.50837254524231</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>1.49220705032349</v>
+        <v>1.4922069311142</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>1.43624901771545</v>
+        <v>1.43624937534332</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G25" t="n">
-        <v>1.41759634017944</v>
+        <v>1.41759657859802</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G27" t="n">
-        <v>1.37158715724945</v>
+        <v>1.37158679962158</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>1.34920370578766</v>
+        <v>1.34920394420624</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>1.46858012676239</v>
+        <v>1.46858024597168</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.39272665977478</v>
+        <v>1.39272677898407</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>1.41137897968292</v>
+        <v>1.41137909889221</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>1.4859893321991</v>
+        <v>1.48598957061768</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G33" t="n">
-        <v>1.4859893321991</v>
+        <v>1.48598957061768</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G34" t="n">
-        <v>1.47852838039398</v>
+        <v>1.47852849960327</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G35" t="n">
-        <v>1.52826857566833</v>
+        <v>1.52826869487762</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.51707720756531</v>
+        <v>1.51707696914673</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.50464165210724</v>
+        <v>1.50464200973511</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>1.52329432964325</v>
+        <v>1.52329468727112</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G39" t="n">
-        <v>1.47355425357819</v>
+        <v>1.4735541343689</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G40" t="n">
-        <v>1.48101544380188</v>
+        <v>1.48101556301117</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G41" t="n">
-        <v>1.52080762386322</v>
+        <v>1.52080774307251</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G42" t="n">
-        <v>1.54194688796997</v>
+        <v>1.54194736480713</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G43" t="n">
-        <v>1.52826857566833</v>
+        <v>1.52826869487762</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G44" t="n">
-        <v>1.53324234485626</v>
+        <v>1.53324270248413</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>1.52329432964325</v>
+        <v>1.52329468727112</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>1.49220705032349</v>
+        <v>1.4922069311142</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G48" t="n">
-        <v>1.44992756843567</v>
+        <v>1.44992780685425</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>1.46111929416656</v>
+        <v>1.46111917495728</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G50" t="n">
-        <v>1.49593722820282</v>
+        <v>1.49593758583069</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G52" t="n">
-        <v>1.53572976589203</v>
+        <v>1.53572964668274</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G53" t="n">
-        <v>1.52329432964325</v>
+        <v>1.52329468727112</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G55" t="n">
-        <v>1.52329432964325</v>
+        <v>1.52329468727112</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G58" t="n">
-        <v>1.54319047927856</v>
+        <v>1.54319071769714</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G59" t="n">
-        <v>1.54070365428925</v>
+        <v>1.54070353507996</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>1.52578163146973</v>
+        <v>1.52578151226044</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.5108597278595</v>
+        <v>1.51085925102234</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G62" t="n">
-        <v>1.52826857566833</v>
+        <v>1.52826869487762</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G63" t="n">
-        <v>1.52080762386322</v>
+        <v>1.52080774307251</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G64" t="n">
-        <v>1.48971998691559</v>
+        <v>1.4897198677063</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.44868397712708</v>
+        <v>1.44868409633636</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G66" t="n">
-        <v>1.38526558876038</v>
+        <v>1.3852653503418</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>1.38029146194458</v>
+        <v>1.38029158115387</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G68" t="n">
-        <v>1.48474586009979</v>
+        <v>1.4847457408905</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G72" t="n">
-        <v>1.54319047927856</v>
+        <v>1.54319071769714</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>1.56681716442108</v>
+        <v>1.56681728363037</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1.6083779335022</v>
+        <v>1.60837757587433</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G76" t="n">
-        <v>1.58521699905396</v>
+        <v>1.58521711826324</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G77" t="n">
-        <v>1.56334328651428</v>
+        <v>1.5633430480957</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G78" t="n">
-        <v>1.58007061481476</v>
+        <v>1.58007025718689</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G79" t="n">
-        <v>1.56334328651428</v>
+        <v>1.5633430480957</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G80" t="n">
-        <v>1.57620990276337</v>
+        <v>1.57621037960052</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G82" t="n">
-        <v>1.58779060840607</v>
+        <v>1.58779072761536</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G83" t="n">
-        <v>1.58521699905396</v>
+        <v>1.58521711826324</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G84" t="n">
-        <v>1.58393037319183</v>
+        <v>1.58393025398254</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G85" t="n">
-        <v>1.58135712146759</v>
+        <v>1.5813570022583</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.56977689266205</v>
+        <v>1.56977665424347</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>1.57620990276337</v>
+        <v>1.57621037960052</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>1.55690932273865</v>
+        <v>1.55690979957581</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G90" t="n">
-        <v>1.53374922275543</v>
+        <v>1.53374910354614</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G93" t="n">
-        <v>1.55304956436157</v>
+        <v>1.55304944515228</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>1.53117573261261</v>
+        <v>1.53117561340332</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.48614084720612</v>
+        <v>1.48614096641541</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G96" t="n">
-        <v>1.42952597141266</v>
+        <v>1.42952609062195</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G98" t="n">
-        <v>1.38577842712402</v>
+        <v>1.38577818870544</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>1.39607179164886</v>
+        <v>1.39607203006744</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G101" t="n">
-        <v>1.4089390039444</v>
+        <v>1.40893912315369</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G105" t="n">
-        <v>1.37677133083344</v>
+        <v>1.37677156925201</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G106" t="n">
-        <v>1.35875749588013</v>
+        <v>1.35875761508942</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.31243598461151</v>
+        <v>1.31243634223938</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G109" t="n">
-        <v>1.30728960037231</v>
+        <v>1.30728948116302</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G112" t="n">
-        <v>1.29056239128113</v>
+        <v>1.29056227207184</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G113" t="n">
-        <v>1.32144296169281</v>
+        <v>1.3214430809021</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>1.28026878833771</v>
+        <v>1.28026866912842</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G115" t="n">
-        <v>1.26675808429718</v>
+        <v>1.26675832271576</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G116" t="n">
-        <v>1.1837660074234</v>
+        <v>1.18376612663269</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G119" t="n">
-        <v>1.10785043239594</v>
+        <v>1.10785055160522</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>1.16446554660797</v>
+        <v>1.16446542739868</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>1.16446554660797</v>
+        <v>1.16446542739868</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>1.09369695186615</v>
+        <v>1.09369707107544</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G125" t="n">
-        <v>1.06152927875519</v>
+        <v>1.06152939796448</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G126" t="n">
-        <v>1.06538963317871</v>
+        <v>1.06538951396942</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G127" t="n">
-        <v>1.06152927875519</v>
+        <v>1.06152939796448</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0904803276062</v>
+        <v>1.09048008918762</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G129" t="n">
-        <v>1.09434020519257</v>
+        <v>1.09434032440186</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G131" t="n">
-        <v>1.04673230648041</v>
+        <v>1.04673206806183</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G132" t="n">
-        <v>1.02936160564423</v>
+        <v>1.02936172485352</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G134" t="n">
-        <v>1.0441586971283</v>
+        <v>1.04415893554688</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>1.12136101722717</v>
+        <v>1.12136089801788</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G139" t="n">
-        <v>1.10978078842163</v>
+        <v>1.10978055000305</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G140" t="n">
-        <v>1.10978078842163</v>
+        <v>1.10978055000305</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.10913741588593</v>
+        <v>1.10913729667664</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.09369695186615</v>
+        <v>1.09369707107544</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G146" t="n">
-        <v>1.09369695186615</v>
+        <v>1.09369707107544</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G147" t="n">
-        <v>1.09562683105469</v>
+        <v>1.09562695026398</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.09691345691681</v>
+        <v>1.0969135761261</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G149" t="n">
-        <v>1.09369695186615</v>
+        <v>1.09369707107544</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G150" t="n">
-        <v>1.09562683105469</v>
+        <v>1.09562695026398</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G151" t="n">
-        <v>1.10913741588593</v>
+        <v>1.10913729667664</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G153" t="n">
-        <v>1.10527718067169</v>
+        <v>1.1052770614624</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G154" t="n">
-        <v>1.10527718067169</v>
+        <v>1.1052770614624</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G159" t="n">
-        <v>1.13358461856842</v>
+        <v>1.13358473777771</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G161" t="n">
-        <v>1.11428415775299</v>
+        <v>1.1142840385437</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.12522101402283</v>
+        <v>1.12522113323212</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1490250825882</v>
+        <v>1.14902496337891</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G166" t="n">
-        <v>1.11878764629364</v>
+        <v>1.11878740787506</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G168" t="n">
-        <v>1.15610194206238</v>
+        <v>1.15610206127167</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.11492741107941</v>
+        <v>1.1149275302887</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G171" t="n">
-        <v>1.11428415775299</v>
+        <v>1.1142840385437</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G174" t="n">
-        <v>1.11943089962006</v>
+        <v>1.11943078041077</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.11943089962006</v>
+        <v>1.11943078041077</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G176" t="n">
-        <v>1.12136101722717</v>
+        <v>1.12136089801788</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G177" t="n">
-        <v>1.14194822311401</v>
+        <v>1.1419483423233</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15803205966949</v>
+        <v>1.15803194046021</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G179" t="n">
-        <v>1.13358461856842</v>
+        <v>1.13358473777771</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G181" t="n">
-        <v>1.14194822311401</v>
+        <v>1.1419483423233</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G182" t="n">
-        <v>1.13808822631836</v>
+        <v>1.13808798789978</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G183" t="n">
-        <v>1.1837660074234</v>
+        <v>1.18376612663269</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G184" t="n">
-        <v>1.2004930973053</v>
+        <v>1.20049321651459</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G185" t="n">
-        <v>1.20306646823883</v>
+        <v>1.20306658744812</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G186" t="n">
-        <v>1.17733263969421</v>
+        <v>1.17733252048492</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G187" t="n">
-        <v>1.17733263969421</v>
+        <v>1.17733252048492</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G188" t="n">
-        <v>1.18119263648987</v>
+        <v>1.18119275569916</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G189" t="n">
-        <v>1.19920635223389</v>
+        <v>1.19920647144318</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>1.16446554660797</v>
+        <v>1.16446542739868</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15095496177673</v>
+        <v>1.15095508098602</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>1.15095496177673</v>
+        <v>1.15095508098602</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G195" t="n">
-        <v>1.13937473297119</v>
+        <v>1.13937485218048</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G198" t="n">
-        <v>1.12200438976288</v>
+        <v>1.12200427055359</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10527718067169</v>
+        <v>1.1052770614624</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>1.09369695186615</v>
+        <v>1.09369707107544</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>1.07503974437714</v>
+        <v>1.07503986358643</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G202" t="n">
-        <v>1.07568299770355</v>
+        <v>1.07568311691284</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>1.13422799110413</v>
+        <v>1.13422787189484</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G210" t="n">
-        <v>1.11943089962006</v>
+        <v>1.11943078041077</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G211" t="n">
-        <v>1.09562683105469</v>
+        <v>1.09562695026398</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G212" t="n">
-        <v>1.08983683586121</v>
+        <v>1.08983671665192</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G213" t="n">
-        <v>1.10785043239594</v>
+        <v>1.10785055160522</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G214" t="n">
-        <v>1.08661997318268</v>
+        <v>1.08661985397339</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G216" t="n">
-        <v>1.06152927875519</v>
+        <v>1.06152939796448</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G217" t="n">
-        <v>1.05509579181671</v>
+        <v>1.05509567260742</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>1.03901195526123</v>
+        <v>1.03901207447052</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G220" t="n">
-        <v>1.06796264648438</v>
+        <v>1.06796276569366</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G222" t="n">
-        <v>1.06152927875519</v>
+        <v>1.06152939796448</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G224" t="n">
-        <v>1.05509579181671</v>
+        <v>1.05509567260742</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>1.03257858753204</v>
+        <v>1.03257846832275</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G227" t="n">
-        <v>1.01392138004303</v>
+        <v>1.01392126083374</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G228" t="n">
-        <v>0.998480975627899</v>
+        <v>0.99848085641861</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G229" t="n">
-        <v>0.997194170951843</v>
+        <v>0.997193992137909</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>1.01199114322662</v>
+        <v>1.01199126243591</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G231" t="n">
-        <v>0.992690622806549</v>
+        <v>0.992690742015839</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>0.990760684013367</v>
+        <v>0.990760743618011</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G233" t="n">
-        <v>1.00427091121674</v>
+        <v>1.00427114963531</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G236" t="n">
-        <v>0.985613942146301</v>
+        <v>0.985613822937012</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>1.00362777709961</v>
+        <v>1.00362765789032</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G238" t="n">
-        <v>1.00748777389526</v>
+        <v>1.00748801231384</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.09369695186615</v>
+        <v>1.09369707107544</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.10334706306458</v>
+        <v>1.10334718227386</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.10334706306458</v>
+        <v>1.10334718227386</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G245" t="n">
-        <v>1.10849392414093</v>
+        <v>1.10849404335022</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G246" t="n">
-        <v>1.10077357292175</v>
+        <v>1.10077369213104</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G247" t="n">
-        <v>1.12457764148712</v>
+        <v>1.12457776069641</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G251" t="n">
-        <v>1.18698298931122</v>
+        <v>1.18698287010193</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G252" t="n">
-        <v>1.17733263969421</v>
+        <v>1.17733252048492</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G255" t="n">
-        <v>1.24938797950745</v>
+        <v>1.24938774108887</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26482808589935</v>
+        <v>1.26482820510864</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32401669025421</v>
+        <v>1.32401657104492</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G262" t="n">
-        <v>1.51444864273071</v>
+        <v>1.51444840431213</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>1.43467307090759</v>
+        <v>1.4346729516983</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G265" t="n">
-        <v>1.43724644184113</v>
+        <v>1.43724632263184</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G267" t="n">
-        <v>1.4514000415802</v>
+        <v>1.45140027999878</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G271" t="n">
-        <v>1.4591201543808</v>
+        <v>1.45912027359009</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G273" t="n">
-        <v>1.43724644184113</v>
+        <v>1.43724632263184</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.45397329330444</v>
+        <v>1.45397353172302</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G277" t="n">
-        <v>1.4526869058609</v>
+        <v>1.45268678665161</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G281" t="n">
-        <v>1.46555399894714</v>
+        <v>1.46555387973785</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G282" t="n">
-        <v>1.46298027038574</v>
+        <v>1.46298038959503</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>1.50801515579224</v>
+        <v>1.50801503658295</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>1.5376091003418</v>
+        <v>1.53760933876038</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>1.56334328651428</v>
+        <v>1.5633430480957</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>1.58907735347748</v>
+        <v>1.58907699584961</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G287" t="n">
-        <v>1.52602887153625</v>
+        <v>1.52602899074554</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G290" t="n">
-        <v>1.47584748268127</v>
+        <v>1.47584736347198</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G291" t="n">
-        <v>1.47970747947693</v>
+        <v>1.47970759868622</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>1.47970747947693</v>
+        <v>1.47970759868622</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>1.47970747947693</v>
+        <v>1.47970759868622</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G297" t="n">
-        <v>1.44367980957031</v>
+        <v>1.44367969036102</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G299" t="n">
-        <v>1.39607179164886</v>
+        <v>1.39607203006744</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G301" t="n">
-        <v>1.4089390039444</v>
+        <v>1.40893912315369</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G303" t="n">
-        <v>1.36390423774719</v>
+        <v>1.36390435695648</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G305" t="n">
-        <v>1.37805783748627</v>
+        <v>1.37805807590485</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>1.37677133083344</v>
+        <v>1.37677156925201</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G308" t="n">
-        <v>1.38963854312897</v>
+        <v>1.38963830471039</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37162446975708</v>
+        <v>1.37162458896637</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G311" t="n">
-        <v>1.41151237487793</v>
+        <v>1.41151225566864</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G312" t="n">
-        <v>1.41408586502075</v>
+        <v>1.41408562660217</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G315" t="n">
-        <v>1.42051911354065</v>
+        <v>1.42051923274994</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>1.45654702186584</v>
+        <v>1.45654678344727</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G317" t="n">
-        <v>1.47070050239563</v>
+        <v>1.47070062160492</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G318" t="n">
-        <v>1.49772143363953</v>
+        <v>1.49772155284882</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G319" t="n">
-        <v>1.49128770828247</v>
+        <v>1.49128794670105</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G323" t="n">
-        <v>1.54918968677521</v>
+        <v>1.54918920993805</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>1.54918968677521</v>
+        <v>1.54918920993805</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.58907735347748</v>
+        <v>1.58907699584961</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G327" t="n">
-        <v>1.6662791967392</v>
+        <v>1.66627931594849</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>1.57489824295044</v>
+        <v>1.57489812374115</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G331" t="n">
-        <v>1.59485030174255</v>
+        <v>1.59485042095184</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56957721710205</v>
+        <v>1.56957733631134</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G333" t="n">
-        <v>1.58819949626923</v>
+        <v>1.58819961547852</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>1.61613285541534</v>
+        <v>1.61613249778748</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G335" t="n">
-        <v>1.55095517635345</v>
+        <v>1.55095565319061</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G337" t="n">
-        <v>1.66534817218781</v>
+        <v>1.66534805297852</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G339" t="n">
-        <v>1.66534817218781</v>
+        <v>1.66534805297852</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66933846473694</v>
+        <v>1.66933870315552</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G348" t="n">
-        <v>1.60150134563446</v>
+        <v>1.60150110721588</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>1.61613285541534</v>
+        <v>1.61613249778748</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>1.62943398952484</v>
+        <v>1.62943434715271</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.68264055252075</v>
+        <v>1.68264031410217</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G357" t="n">
-        <v>1.69062125682831</v>
+        <v>1.69062113761902</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G358" t="n">
-        <v>1.67997980117798</v>
+        <v>1.67997992038727</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G360" t="n">
-        <v>1.68397045135498</v>
+        <v>1.68397033214569</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68264055252075</v>
+        <v>1.68264031410217</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G363" t="n">
-        <v>1.65736746788025</v>
+        <v>1.65736758708954</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G364" t="n">
-        <v>1.6866307258606</v>
+        <v>1.68663084506989</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G367" t="n">
-        <v>1.69461190700531</v>
+        <v>1.69461154937744</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>1.68264055252075</v>
+        <v>1.68264031410217</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G369" t="n">
-        <v>1.69461190700531</v>
+        <v>1.69461154937744</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70126259326935</v>
+        <v>1.70126235485077</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G373" t="n">
-        <v>1.66667830944061</v>
+        <v>1.66667854785919</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G376" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259237289429</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G377" t="n">
-        <v>1.70791292190552</v>
+        <v>1.7079131603241</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G378" t="n">
-        <v>1.72254455089569</v>
+        <v>1.72254478931427</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G379" t="n">
-        <v>1.71323382854462</v>
+        <v>1.71323359012604</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259237289429</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G382" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259237289429</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259237289429</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259237289429</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G385" t="n">
-        <v>1.66933846473694</v>
+        <v>1.66933870315552</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G386" t="n">
-        <v>1.68530035018921</v>
+        <v>1.68530058860779</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G387" t="n">
-        <v>1.67332923412323</v>
+        <v>1.67332911491394</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G388" t="n">
-        <v>1.67332923412323</v>
+        <v>1.67332911491394</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G389" t="n">
-        <v>1.65470707416534</v>
+        <v>1.65470695495605</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G394" t="n">
-        <v>1.68397045135498</v>
+        <v>1.68397033214569</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G395" t="n">
-        <v>1.69195139408112</v>
+        <v>1.69195115566254</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.71057343482971</v>
+        <v>1.71057331562042</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G397" t="n">
-        <v>1.72254455089569</v>
+        <v>1.72254478931427</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G398" t="n">
-        <v>1.70126259326935</v>
+        <v>1.70126235485077</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259237289429</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G401" t="n">
-        <v>1.70791292190552</v>
+        <v>1.7079131603241</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G402" t="n">
-        <v>1.69727218151093</v>
+        <v>1.69727170467377</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G405" t="n">
-        <v>1.65736746788025</v>
+        <v>1.65736758708954</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G406" t="n">
-        <v>1.66401839256287</v>
+        <v>1.66401815414429</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G409" t="n">
-        <v>1.67864954471588</v>
+        <v>1.67864990234375</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G410" t="n">
-        <v>1.69993197917938</v>
+        <v>1.69993233680725</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G411" t="n">
-        <v>1.70126259326935</v>
+        <v>1.70126235485077</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68264055252075</v>
+        <v>1.68264031410217</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G413" t="n">
-        <v>1.66401839256287</v>
+        <v>1.66401815414429</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G414" t="n">
-        <v>1.64007520675659</v>
+        <v>1.64007544517517</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G415" t="n">
-        <v>1.64007520675659</v>
+        <v>1.64007544517517</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G416" t="n">
-        <v>1.65470707416534</v>
+        <v>1.65470695495605</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G417" t="n">
-        <v>1.66534817218781</v>
+        <v>1.66534805297852</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G418" t="n">
-        <v>1.65204691886902</v>
+        <v>1.65204668045044</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G419" t="n">
-        <v>1.67199909687042</v>
+        <v>1.67199897766113</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.65204691886902</v>
+        <v>1.65204668045044</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>1.68397045135498</v>
+        <v>1.68397033214569</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G422" t="n">
-        <v>1.67997980117798</v>
+        <v>1.67997992038727</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>1.66933846473694</v>
+        <v>1.66933870315552</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G427" t="n">
-        <v>1.63342499732971</v>
+        <v>1.63342475891113</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>1.62278366088867</v>
+        <v>1.62278342247009</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G429" t="n">
-        <v>1.61480259895325</v>
+        <v>1.61480271816254</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G431" t="n">
-        <v>1.55893647670746</v>
+        <v>1.55893635749817</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G432" t="n">
-        <v>1.56824743747711</v>
+        <v>1.5682475566864</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G433" t="n">
-        <v>1.55361568927765</v>
+        <v>1.55361557006836</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G435" t="n">
-        <v>1.53765392303467</v>
+        <v>1.53765380382538</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G438" t="n">
-        <v>1.51504147052765</v>
+        <v>1.51504123210907</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G440" t="n">
-        <v>1.51637125015259</v>
+        <v>1.51637160778046</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G441" t="n">
-        <v>1.5416442155838</v>
+        <v>1.54164433479309</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G443" t="n">
-        <v>1.5429744720459</v>
+        <v>1.54297435283661</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G445" t="n">
-        <v>1.51637125015259</v>
+        <v>1.51637160778046</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G448" t="n">
-        <v>1.64406597614288</v>
+        <v>1.64406585693359</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G449" t="n">
-        <v>1.68131017684937</v>
+        <v>1.68131005764008</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G450" t="n">
-        <v>1.65603721141815</v>
+        <v>1.65603733062744</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G451" t="n">
-        <v>1.66002762317657</v>
+        <v>1.660027384758</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>1.66933846473694</v>
+        <v>1.66933870315552</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G453" t="n">
-        <v>1.67332923412323</v>
+        <v>1.67332911491394</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G454" t="n">
-        <v>1.68264055252075</v>
+        <v>1.68264031410217</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G456" t="n">
-        <v>1.68397045135498</v>
+        <v>1.68397033214569</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G457" t="n">
-        <v>1.63874518871307</v>
+        <v>1.63874530792236</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G460" t="n">
-        <v>1.58819949626923</v>
+        <v>1.58819961547852</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>1.57622802257538</v>
+        <v>1.57622790336609</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G462" t="n">
-        <v>1.55627572536469</v>
+        <v>1.55627608299255</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G463" t="n">
-        <v>1.56824743747711</v>
+        <v>1.5682475566864</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G464" t="n">
-        <v>1.57223796844482</v>
+        <v>1.57223773002625</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>1.60948157310486</v>
+        <v>1.60948216915131</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58952963352203</v>
+        <v>1.58952987194061</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>1.62943398952484</v>
+        <v>1.62943434715271</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G473" t="n">
-        <v>1.65337717533112</v>
+        <v>1.65337705612183</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.64938616752625</v>
+        <v>1.64938640594482</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58952963352203</v>
+        <v>1.58952987194061</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>1.58952963352203</v>
+        <v>1.58952987194061</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G478" t="n">
-        <v>1.57888853549957</v>
+        <v>1.57888865470886</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61613285541534</v>
+        <v>1.61613249778748</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G484" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G485" t="n">
-        <v>1.52568256855011</v>
+        <v>1.52568244934082</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25</v>
       </c>
       <c r="G486" t="n">
-        <v>1.49641931056976</v>
+        <v>1.49641919136047</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.49641931056976</v>
+        <v>1.49641919136047</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G488" t="n">
-        <v>1.53765392303467</v>
+        <v>1.53765380382538</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G489" t="n">
-        <v>1.57356798648834</v>
+        <v>1.57356774806976</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G490" t="n">
-        <v>1.53366339206696</v>
+        <v>1.53366351127625</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G491" t="n">
-        <v>1.56957721710205</v>
+        <v>1.56957733631134</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>1.59618055820465</v>
+        <v>1.59618043899536</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>1.54962491989136</v>
+        <v>1.54962515830994</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>1.57622802257538</v>
+        <v>1.57622790336609</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G495" t="n">
-        <v>1.57622802257538</v>
+        <v>1.57622790336609</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>1.57622802257538</v>
+        <v>1.57622790336609</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G497" t="n">
-        <v>1.5429744720459</v>
+        <v>1.54297435283661</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G499" t="n">
-        <v>1.5429744720459</v>
+        <v>1.54297435283661</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.51637125015259</v>
+        <v>1.51637160778046</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G501" t="n">
-        <v>1.51238083839417</v>
+        <v>1.51238107681274</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G503" t="n">
-        <v>1.51105082035065</v>
+        <v>1.51105070114136</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G504" t="n">
-        <v>1.52568256855011</v>
+        <v>1.52568244934082</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G507" t="n">
-        <v>1.48976862430573</v>
+        <v>1.48976850509644</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G510" t="n">
-        <v>1.49375879764557</v>
+        <v>1.49375891685486</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G511" t="n">
-        <v>1.5283430814743</v>
+        <v>1.52834272384644</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G512" t="n">
-        <v>1.49109864234924</v>
+        <v>1.49109852313995</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.25</v>
       </c>
       <c r="G513" t="n">
-        <v>1.49641931056976</v>
+        <v>1.49641919136047</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G514" t="n">
-        <v>1.50306975841522</v>
+        <v>1.50306987762451</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G516" t="n">
-        <v>1.5429744720459</v>
+        <v>1.54297435283661</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G517" t="n">
-        <v>1.51637125015259</v>
+        <v>1.51637160778046</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>1.54962491989136</v>
+        <v>1.54962515830994</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G522" t="n">
-        <v>1.55627572536469</v>
+        <v>1.55627608299255</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>1.5429744720459</v>
+        <v>1.54297435283661</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>1.54962491989136</v>
+        <v>1.54962515830994</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G526" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G528" t="n">
-        <v>1.53632354736328</v>
+        <v>1.53632366657257</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.57622802257538</v>
+        <v>1.57622790336609</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.55627572536469</v>
+        <v>1.55627608299255</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G532" t="n">
-        <v>1.55627572536469</v>
+        <v>1.55627608299255</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G533" t="n">
-        <v>1.5429744720459</v>
+        <v>1.54297435283661</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48976862430573</v>
+        <v>1.48976850509644</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>1.44321310520172</v>
+        <v>1.44321346282959</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>1.42326092720032</v>
+        <v>1.42326104640961</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>1.42991161346436</v>
+        <v>1.42991173267365</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>1.44321310520172</v>
+        <v>1.44321346282959</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.45651471614838</v>
+        <v>1.45651459693909</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>1.44321310520172</v>
+        <v>1.44321346282959</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>1.43656265735626</v>
+        <v>1.43656253814697</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G552" t="n">
-        <v>1.3767055273056</v>
+        <v>1.37670564651489</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>1.41661024093628</v>
+        <v>1.41661036014557</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>1.40330851078033</v>
+        <v>1.40330862998962</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G556" t="n">
-        <v>1.40330851078033</v>
+        <v>1.40330862998962</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G557" t="n">
-        <v>1.40330851078033</v>
+        <v>1.40330862998962</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G558" t="n">
-        <v>1.40330851078033</v>
+        <v>1.40330862998962</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G560" t="n">
-        <v>1.47646701335907</v>
+        <v>1.47646689414978</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.47646701335907</v>
+        <v>1.47646689414978</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G565" t="n">
-        <v>1.45651471614838</v>
+        <v>1.45651459693909</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>1.42991161346436</v>
+        <v>1.42991173267365</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G571" t="n">
-        <v>1.45651471614838</v>
+        <v>1.45651459693909</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>1.45651471614838</v>
+        <v>1.45651459693909</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.48413848876953</v>
+        <v>1.48413860797882</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G576" t="n">
-        <v>1.48413848876953</v>
+        <v>1.48413860797882</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G577" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G578" t="n">
-        <v>1.53988063335419</v>
+        <v>1.53988075256348</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.51200950145721</v>
+        <v>1.51200985908508</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G580" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>1.51200950145721</v>
+        <v>1.51200985908508</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G583" t="n">
-        <v>1.54684865474701</v>
+        <v>1.54684853553772</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.58168733119965</v>
+        <v>1.58168745040894</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.5747195482254</v>
+        <v>1.57471966743469</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>1.60955846309662</v>
+        <v>1.60955858230591</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G589" t="n">
-        <v>1.64439725875854</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G590" t="n">
-        <v>1.64439725875854</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>1.63742971420288</v>
+        <v>1.63742983341217</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G592" t="n">
-        <v>1.65833330154419</v>
+        <v>1.6583331823349</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G593" t="n">
-        <v>1.64439725875854</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G595" t="n">
-        <v>1.65833330154419</v>
+        <v>1.6583331823349</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>1.66530072689056</v>
+        <v>1.66530084609985</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G598" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64439725875854</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>1.66530072689056</v>
+        <v>1.66530084609985</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>1.63742971420288</v>
+        <v>1.63742983341217</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>1.65833330154419</v>
+        <v>1.6583331823349</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G604" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>1.63046169281006</v>
+        <v>1.63046205043793</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G606" t="n">
-        <v>1.60955846309662</v>
+        <v>1.60955858230591</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>1.5747195482254</v>
+        <v>1.57471966743469</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>1.55381643772125</v>
+        <v>1.55381631851196</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>1.54684865474701</v>
+        <v>1.54684853553772</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.55381643772125</v>
+        <v>1.55381631851196</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>1.55381643772125</v>
+        <v>1.55381631851196</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.51200950145721</v>
+        <v>1.51200985908508</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G613" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G614" t="n">
-        <v>1.38658952713013</v>
+        <v>1.38658940792084</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G619" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>1.4283961057663</v>
+        <v>1.42839598655701</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>1.49110627174377</v>
+        <v>1.49110639095306</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>1.48413848876953</v>
+        <v>1.48413860797882</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G631" t="n">
-        <v>1.477170586586</v>
+        <v>1.47717046737671</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G635" t="n">
-        <v>1.4283961057663</v>
+        <v>1.42839598655701</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G637" t="n">
-        <v>1.49110627174377</v>
+        <v>1.49110639095306</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G639" t="n">
-        <v>1.49110627174377</v>
+        <v>1.49110639095306</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>1.48413848876953</v>
+        <v>1.48413860797882</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G641" t="n">
-        <v>1.477170586586</v>
+        <v>1.47717046737671</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G642" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>1.51200950145721</v>
+        <v>1.51200985908508</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G645" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G647" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G649" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G650" t="n">
-        <v>1.51200950145721</v>
+        <v>1.51200985908508</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.50504195690155</v>
+        <v>1.50504183769226</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G654" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G655" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G657" t="n">
-        <v>1.50504195690155</v>
+        <v>1.50504183769226</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G658" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G659" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G660" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G661" t="n">
-        <v>1.51200950145721</v>
+        <v>1.51200985908508</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G662" t="n">
-        <v>1.50504195690155</v>
+        <v>1.50504183769226</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G663" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G664" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G665" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G666" t="n">
-        <v>1.50504195690155</v>
+        <v>1.50504183769226</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>1.49807393550873</v>
+        <v>1.49807405471802</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G668" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G669" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G670" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G673" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G675" t="n">
-        <v>1.477170586586</v>
+        <v>1.47717046737671</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>1.41446053981781</v>
+        <v>1.41446042060852</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G682" t="n">
-        <v>1.42142808437347</v>
+        <v>1.42142832279205</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.41446053981781</v>
+        <v>1.41446042060852</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G684" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G685" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G686" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>1.42142808437347</v>
+        <v>1.42142832279205</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G689" t="n">
-        <v>1.4283961057663</v>
+        <v>1.42839598655701</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G691" t="n">
-        <v>1.4283961057663</v>
+        <v>1.42839598655701</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G693" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G695" t="n">
-        <v>1.44233155250549</v>
+        <v>1.44233167171478</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G696" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G697" t="n">
-        <v>1.47020280361176</v>
+        <v>1.47020268440247</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G699" t="n">
-        <v>1.51897740364075</v>
+        <v>1.51897752285004</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G700" t="n">
-        <v>1.52594530582428</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G702" t="n">
-        <v>1.4283961057663</v>
+        <v>1.42839598655701</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>1.42142808437347</v>
+        <v>1.42142832279205</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.4283961057663</v>
+        <v>1.42839598655701</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G707" t="n">
-        <v>1.32387936115265</v>
+        <v>1.32387948036194</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.34478282928467</v>
+        <v>1.3447824716568</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G710" t="n">
-        <v>1.32387936115265</v>
+        <v>1.32387948036194</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.35523462295532</v>
+        <v>1.35523450374603</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G712" t="n">
-        <v>1.36220228672028</v>
+        <v>1.36220240592957</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G713" t="n">
-        <v>1.37265396118164</v>
+        <v>1.37265384197235</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G720" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G721" t="n">
-        <v>1.1845235824585</v>
+        <v>1.18452382087708</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G724" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G726" t="n">
-        <v>1.28904044628143</v>
+        <v>1.28904032707214</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G728" t="n">
-        <v>1.28904044628143</v>
+        <v>1.28904032707214</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30297589302063</v>
+        <v>1.30297601222992</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G731" t="n">
-        <v>1.27162098884583</v>
+        <v>1.27162086963654</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G732" t="n">
-        <v>1.31342768669128</v>
+        <v>1.31342780590057</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G733" t="n">
-        <v>1.30994391441345</v>
+        <v>1.30994367599487</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G734" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G737" t="n">
-        <v>1.22284662723541</v>
+        <v>1.22284638881683</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.1845235824585</v>
+        <v>1.18452382087708</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G742" t="n">
-        <v>1.26465332508087</v>
+        <v>1.26465320587158</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>1.24723362922668</v>
+        <v>1.24723374843597</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.23678207397461</v>
+        <v>1.23678195476532</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G759" t="n">
-        <v>1.27162098884583</v>
+        <v>1.27162086963654</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>1.20542693138123</v>
+        <v>1.20542705059052</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>1.20542693138123</v>
+        <v>1.20542705059052</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>1.19149160385132</v>
+        <v>1.19149136543274</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.1845235824585</v>
+        <v>1.18452382087708</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G766" t="n">
-        <v>1.20542693138123</v>
+        <v>1.20542705059052</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G771" t="n">
-        <v>1.23678207397461</v>
+        <v>1.23678195476532</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>1.24723362922668</v>
+        <v>1.24723374843597</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G773" t="n">
-        <v>1.1845235824585</v>
+        <v>1.18452382087708</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.23678207397461</v>
+        <v>1.23678195476532</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G778" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>1.24723362922668</v>
+        <v>1.24723374843597</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.24723362922668</v>
+        <v>1.24723374843597</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G785" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G787" t="n">
-        <v>1.25768530368805</v>
+        <v>1.25768542289734</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G788" t="n">
-        <v>1.25768530368805</v>
+        <v>1.25768542289734</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>1.24723362922668</v>
+        <v>1.24723374843597</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G794" t="n">
-        <v>1.32387936115265</v>
+        <v>1.32387948036194</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.30297589302063</v>
+        <v>1.30297601222992</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G797" t="n">
-        <v>1.28904044628143</v>
+        <v>1.28904032707214</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>1.32736325263977</v>
+        <v>1.32736313343048</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G799" t="n">
-        <v>1.31342768669128</v>
+        <v>1.31342780590057</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G800" t="n">
-        <v>1.32736325263977</v>
+        <v>1.32736313343048</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G802" t="n">
-        <v>1.31342768669128</v>
+        <v>1.31342780590057</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G803" t="n">
-        <v>1.34129881858826</v>
+        <v>1.34129869937897</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G804" t="n">
-        <v>1.32736325263977</v>
+        <v>1.32736313343048</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G805" t="n">
-        <v>1.34129881858826</v>
+        <v>1.34129869937897</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G806" t="n">
-        <v>1.35523462295532</v>
+        <v>1.35523450374603</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G809" t="n">
-        <v>1.34478282928467</v>
+        <v>1.3447824716568</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G810" t="n">
-        <v>1.34478282928467</v>
+        <v>1.3447824716568</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G813" t="n">
-        <v>1.35523462295532</v>
+        <v>1.35523450374603</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>1.37265396118164</v>
+        <v>1.37265384197235</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G816" t="n">
-        <v>1.37265396118164</v>
+        <v>1.37265384197235</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G819" t="n">
-        <v>1.38658952713013</v>
+        <v>1.38658940792084</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G825" t="n">
-        <v>1.37265396118164</v>
+        <v>1.37265384197235</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G827" t="n">
-        <v>1.44430613517761</v>
+        <v>1.4443062543869</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G829" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G831" t="n">
-        <v>1.44430613517761</v>
+        <v>1.4443062543869</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G839" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G840" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G845" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G854" t="n">
-        <v>1.42975389957428</v>
+        <v>1.42975401878357</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G856" t="n">
-        <v>1.42975389957428</v>
+        <v>1.42975401878357</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.43339216709137</v>
+        <v>1.43339204788208</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G858" t="n">
-        <v>1.40792572498322</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G859" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G860" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G862" t="n">
-        <v>1.41883981227875</v>
+        <v>1.41883969306946</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38609731197357</v>
+        <v>1.38609719276428</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G864" t="n">
-        <v>1.36063098907471</v>
+        <v>1.360631108284</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G866" t="n">
-        <v>1.36063098907471</v>
+        <v>1.360631108284</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G867" t="n">
-        <v>1.37154507637024</v>
+        <v>1.37154519557953</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G870" t="n">
-        <v>1.37154507637024</v>
+        <v>1.37154519557953</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G871" t="n">
-        <v>1.35335493087769</v>
+        <v>1.3533548116684</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G872" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.37518334388733</v>
+        <v>1.37518310546875</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.38609731197357</v>
+        <v>1.38609719276428</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G875" t="n">
-        <v>1.41520178318024</v>
+        <v>1.41520166397095</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G876" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247796058655</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.43339216709137</v>
+        <v>1.43339204788208</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G879" t="n">
-        <v>1.42975389957428</v>
+        <v>1.42975401878357</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G883" t="n">
-        <v>1.43339216709137</v>
+        <v>1.43339204788208</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G884" t="n">
-        <v>1.42975389957428</v>
+        <v>1.42975401878357</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G885" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G886" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247796058655</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G888" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G889" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.45158231258392</v>
+        <v>1.45158219337463</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G908" t="n">
-        <v>1.41883981227875</v>
+        <v>1.41883969306946</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G910" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247796058655</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G915" t="n">
-        <v>1.43339216709137</v>
+        <v>1.43339204788208</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>1.43339216709137</v>
+        <v>1.43339204788208</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.40792572498322</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>1.40792572498322</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G922" t="n">
-        <v>1.41883981227875</v>
+        <v>1.41883969306946</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G923" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247796058655</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G924" t="n">
-        <v>1.38609731197357</v>
+        <v>1.38609719276428</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>1.37882137298584</v>
+        <v>1.37882125377655</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.38609731197357</v>
+        <v>1.38609719276428</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>1.40792572498322</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G930" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G932" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G934" t="n">
-        <v>1.37518334388733</v>
+        <v>1.37518310546875</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.37882137298584</v>
+        <v>1.37882125377655</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G936" t="n">
-        <v>1.40792572498322</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G937" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G938" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G939" t="n">
-        <v>1.38973522186279</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>1.39337337017059</v>
+        <v>1.39337348937988</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>1.39337337017059</v>
+        <v>1.39337348937988</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>1.39337337017059</v>
+        <v>1.39337348937988</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G947" t="n">
-        <v>1.37518334388733</v>
+        <v>1.37518310546875</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G950" t="n">
-        <v>1.38609731197357</v>
+        <v>1.38609719276428</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G951" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G956" t="n">
-        <v>1.41520178318024</v>
+        <v>1.41520166397095</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.41520178318024</v>
+        <v>1.41520166397095</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G964" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247796058655</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G966" t="n">
-        <v>1.42975389957428</v>
+        <v>1.42975401878357</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.44430613517761</v>
+        <v>1.4443062543869</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G971" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G974" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G976" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G977" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G978" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G979" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G980" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G982" t="n">
-        <v>1.56436192989349</v>
+        <v>1.5643618106842</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>1.59346628189087</v>
+        <v>1.59346640110016</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G988" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G989" t="n">
-        <v>1.6007422208786</v>
+        <v>1.60074234008789</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G990" t="n">
-        <v>1.59346628189087</v>
+        <v>1.59346640110016</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G992" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.25</v>
       </c>
       <c r="G996" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.25</v>
       </c>
       <c r="G997" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.25</v>
       </c>
       <c r="G999" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.25</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.76081657409668</v>
+        <v>1.76081681251526</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.78992092609406</v>
+        <v>1.78992116451263</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.81174945831299</v>
+        <v>1.81174957752228</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.78264474868774</v>
+        <v>1.78264498710632</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.78992092609406</v>
+        <v>1.78992116451263</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.77536880970001</v>
+        <v>1.77536869049072</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.82630145549774</v>
+        <v>1.82630157470703</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.81902551651001</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.81174945831299</v>
+        <v>1.81174957752228</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.84812951087952</v>
+        <v>1.84812998771667</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.90633833408356</v>
+        <v>1.90633845329285</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.91361463069916</v>
+        <v>1.91361486911774</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.88451015949249</v>
+        <v>1.88451027870178</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.90633833408356</v>
+        <v>1.90633845329285</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.98637580871582</v>
+        <v>1.98637557029724</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08096504211426</v>
+        <v>2.08096480369568</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.11734557151794</v>
+        <v>2.11734533309937</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.08096504211426</v>
+        <v>2.08096480369568</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.08096504211426</v>
+        <v>2.08096480369568</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.13917398452759</v>
+        <v>2.13917374610901</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.12462186813354</v>
+        <v>2.12462162971497</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.32835245132446</v>
+        <v>2.32835268974304</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.29197192192078</v>
+        <v>2.29197216033936</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.29197192192078</v>
+        <v>2.29197216033936</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.32835245132446</v>
+        <v>2.32835268974304</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.08096504211426</v>
+        <v>2.08096480369568</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.14645004272461</v>
+        <v>2.14644980430603</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.05913686752319</v>
+        <v>2.05913662910461</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.00820374488831</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.00820374488831</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.89906239509583</v>
+        <v>1.8990626335144</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.01548004150391</v>
+        <v>2.01548027992249</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.86268198490143</v>
+        <v>1.86268186569214</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.01548004150391</v>
+        <v>2.01548027992249</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.93544316291809</v>
+        <v>1.93544292449951</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.94999527931213</v>
+        <v>1.94999551773071</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.03003215789795</v>
+        <v>2.03003239631653</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.01548004150391</v>
+        <v>2.01548027992249</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.03003215789795</v>
+        <v>2.03003239631653</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.04458427429199</v>
+        <v>2.04458475112915</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.05913686752319</v>
+        <v>2.05913662910461</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.12462186813354</v>
+        <v>2.12462162971497</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.12462186813354</v>
+        <v>2.12462162971497</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.13917398452759</v>
+        <v>2.13917374610901</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.19738268852234</v>
+        <v>2.19738292694092</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.24103951454163</v>
+        <v>2.24103927612305</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.93544316291809</v>
+        <v>1.93544292449951</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.91361463069916</v>
+        <v>1.91361486911774</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.99365186691284</v>
+        <v>1.99365162849426</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.86995816230774</v>
+        <v>1.86995792388916</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.90633833408356</v>
+        <v>1.90633845329285</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.84812951087952</v>
+        <v>1.84812998771667</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.85540580749512</v>
+        <v>1.85540616512299</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.5</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.81902551651001</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>2.5</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.81902551651001</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.84812951087952</v>
+        <v>1.84812998771667</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>2.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.81902551651001</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.680779337883</v>
+        <v>1.68077957630157</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.6880556344986</v>
+        <v>1.68805539608002</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.7389885187149</v>
+        <v>1.73898839950562</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.75354075431824</v>
+        <v>1.75354051589966</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.78264474868774</v>
+        <v>1.78264498710632</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.78992092609406</v>
+        <v>1.78992116451263</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.84812951087952</v>
+        <v>1.84812998771667</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.81902551651001</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.78264474868774</v>
+        <v>1.78264498710632</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.75354075431824</v>
+        <v>1.75354051589966</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.67350351810455</v>
+        <v>1.67350327968597</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.680779337883</v>
+        <v>1.68077957630157</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>2.25</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.6080185174942</v>
+        <v>1.60801839828491</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.6080185174942</v>
+        <v>1.60801839828491</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.57891404628754</v>
+        <v>1.57891416549683</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.25</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.25</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.6080185174942</v>
+        <v>1.60801839828491</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.6007422208786</v>
+        <v>1.60074234008789</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.57891404628754</v>
+        <v>1.57891416549683</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.59346628189087</v>
+        <v>1.59346640110016</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.58619034290314</v>
+        <v>1.58619022369385</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.58619034290314</v>
+        <v>1.58619022369385</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.57891404628754</v>
+        <v>1.57891416549683</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.75354075431824</v>
+        <v>1.75354051589966</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.7244359254837</v>
+        <v>1.72443604469299</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69533157348633</v>
+        <v>1.69533169269562</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.680779337883</v>
+        <v>1.68077957630157</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.6080185174942</v>
+        <v>1.60801839828491</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.57891404628754</v>
+        <v>1.57891416549683</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74626433849335</v>
+        <v>1.74626445770264</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.7389885187149</v>
+        <v>1.73898839950562</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.7244359254837</v>
+        <v>1.72443604469299</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.69533157348633</v>
+        <v>1.69533169269562</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.67350351810455</v>
+        <v>1.67350327968597</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.69533157348633</v>
+        <v>1.69533169269562</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.67350351810455</v>
+        <v>1.67350327968597</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.65895092487335</v>
+        <v>1.65895140171051</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.25</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>2.25</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.25</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.25</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.63712310791016</v>
+        <v>1.63712298870087</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.6007422208786</v>
+        <v>1.60074234008789</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.6007422208786</v>
+        <v>1.60074234008789</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.6007422208786</v>
+        <v>1.60074234008789</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.61529457569122</v>
+        <v>1.6152948141098</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.55708563327789</v>
+        <v>1.55708575248718</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.46249616146088</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.47704863548279</v>
+        <v>1.47704875469208</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.54980969429016</v>
+        <v>1.54980981349945</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.49160075187683</v>
+        <v>1.49160087108612</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247796058655</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.39337337017059</v>
+        <v>1.39337348937988</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.40064966678619</v>
+        <v>1.4006495475769</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.35335493087769</v>
+        <v>1.3533548116684</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.42611587047577</v>
+        <v>1.42611610889435</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.37518334388733</v>
+        <v>1.37518310546875</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.44430613517761</v>
+        <v>1.4443062543869</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.6007422208786</v>
+        <v>1.60074234008789</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.78264474868774</v>
+        <v>1.78264498710632</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.7389885187149</v>
+        <v>1.73898839950562</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.7244359254837</v>
+        <v>1.72443604469299</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.7389885187149</v>
+        <v>1.73898839950562</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.78992092609406</v>
+        <v>1.78992116451263</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.77536880970001</v>
+        <v>1.77536869049072</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.76081657409668</v>
+        <v>1.76081681251526</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.78264474868774</v>
+        <v>1.78264498710632</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.75354075431824</v>
+        <v>1.75354051589966</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.81902551651001</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.86268198490143</v>
+        <v>1.86268186569214</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.88451015949249</v>
+        <v>1.88451027870178</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.85540580749512</v>
+        <v>1.85540616512299</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.84812951087952</v>
+        <v>1.84812998771667</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.86995816230774</v>
+        <v>1.86995792388916</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.78992092609406</v>
+        <v>1.78992116451263</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.81174945831299</v>
+        <v>1.81174957752228</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.85540580749512</v>
+        <v>1.85540616512299</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.86268198490143</v>
+        <v>1.86268186569214</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.89906239509583</v>
+        <v>1.8990626335144</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.90633833408356</v>
+        <v>1.90633845329285</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.90633833408356</v>
+        <v>1.90633845329285</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.84085369110107</v>
+        <v>1.84085357189178</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.81174945831299</v>
+        <v>1.81174957752228</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.81174945831299</v>
+        <v>1.81174957752228</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.81174945831299</v>
+        <v>1.81174957752228</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.74626433849335</v>
+        <v>1.74626445770264</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.7389885187149</v>
+        <v>1.73898839950562</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.7389885187149</v>
+        <v>1.73898839950562</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.70988368988037</v>
+        <v>1.70988380908966</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.77536880970001</v>
+        <v>1.77536869049072</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.99365186691284</v>
+        <v>1.99365162849426</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.05913686752319</v>
+        <v>2.05913662910461</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.99365186691284</v>
+        <v>1.99365162849426</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.99365186691284</v>
+        <v>1.99365162849426</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.91361463069916</v>
+        <v>1.91361486911774</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.86995816230774</v>
+        <v>1.86995792388916</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.89906239509583</v>
+        <v>1.8990626335144</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.84812951087952</v>
+        <v>1.84812998771667</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.89906239509583</v>
+        <v>1.8990626335144</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.03003215789795</v>
+        <v>2.03003239631653</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.00820374488831</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.00820374488831</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.06641292572021</v>
+        <v>2.06641268730164</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.06641292572021</v>
+        <v>2.06641268730164</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.03003215789795</v>
+        <v>2.03003239631653</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.99365186691284</v>
+        <v>1.99365162849426</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.00820374488831</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.03003215789795</v>
+        <v>2.03003239631653</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.03003215789795</v>
+        <v>2.03003239631653</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.06641292572021</v>
+        <v>2.06641268730164</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.04458427429199</v>
+        <v>2.04458475112915</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.04458427429199</v>
+        <v>2.04458475112915</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.01548004150391</v>
+        <v>2.01548027992249</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.99365186691284</v>
+        <v>1.99365162849426</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.00820374488831</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454751491547</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.94999527931213</v>
+        <v>1.94999551773071</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.98637580871582</v>
+        <v>1.98637557029724</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.05913686752319</v>
+        <v>2.05913662910461</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.09484601020813</v>
+        <v>2.09484624862671</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.09484601020813</v>
+        <v>2.09484624862671</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.46013951301575</v>
+        <v>2.46013927459717</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.46013951301575</v>
+        <v>2.46013927459717</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.45268440246582</v>
+        <v>2.45268487930298</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.47504925727844</v>
+        <v>2.47504949569702</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.37067985534668</v>
+        <v>2.3706796169281</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>2.33340525627136</v>
+        <v>2.33340501785278</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1367" t="n">
-        <v>2.31849503517151</v>
+        <v>2.31849527359009</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1370" t="n">
-        <v>2.31849503517151</v>
+        <v>2.31849527359009</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.30358505249023</v>
+        <v>2.30358529090881</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.50486946105957</v>
+        <v>2.50486898422241</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1376" t="n">
-        <v>2.65396857261658</v>
+        <v>2.65396881103516</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.68378877639771</v>
+        <v>2.68378829956055</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.5</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.60923886299133</v>
+        <v>2.60923910140991</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.54959940910339</v>
+        <v>2.54959917068481</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>2.60923886299133</v>
+        <v>2.60923910140991</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1384" t="n">
-        <v>2.53468942642212</v>
+        <v>2.53468918800354</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.46013951301575</v>
+        <v>2.46013927459717</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.52723455429077</v>
+        <v>2.52723407745361</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.44522953033447</v>
+        <v>2.44522929191589</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.36322498321533</v>
+        <v>2.36322522163391</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.33340525627136</v>
+        <v>2.33340501785278</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.33340525627136</v>
+        <v>2.33340501785278</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.40050005912781</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.37067985534668</v>
+        <v>2.3706796169281</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>2.40050005912781</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1412" t="n">
-        <v>2.33340525627136</v>
+        <v>2.33340501785278</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1416" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.30358505249023</v>
+        <v>2.30358529090881</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.44522953033447</v>
+        <v>2.44522929191589</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.44522953033447</v>
+        <v>2.44522929191589</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.46013951301575</v>
+        <v>2.46013927459717</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.37067985534668</v>
+        <v>2.3706796169281</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.40050005912781</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.37067985534668</v>
+        <v>2.3706796169281</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.37067985534668</v>
+        <v>2.3706796169281</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.40050005912781</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.40050005912781</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.34086036682129</v>
+        <v>2.34086012840271</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.45268440246582</v>
+        <v>2.45268487930298</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.43777465820312</v>
+        <v>2.43777441978455</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.39304494857788</v>
+        <v>2.39304447174072</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.40050005912781</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.43777465820312</v>
+        <v>2.43777441978455</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.36322498321533</v>
+        <v>2.36322522163391</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.40875720977783</v>
+        <v>2.40875744819641</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.40875720977783</v>
+        <v>2.40875744819641</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.43915200233459</v>
+        <v>2.43915152549744</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.43915200233459</v>
+        <v>2.43915152549744</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.43915200233459</v>
+        <v>2.43915152549744</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.46194744110107</v>
+        <v>2.4619472026825</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.25</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.4695463180542</v>
+        <v>2.46954607963562</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.25</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.4695463180542</v>
+        <v>2.46954607963562</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.25</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.4695463180542</v>
+        <v>2.46954607963562</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.46194744110107</v>
+        <v>2.4619472026825</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.40875720977783</v>
+        <v>2.40875744819641</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.28717970848083</v>
+        <v>2.28717947006226</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.28717970848083</v>
+        <v>2.28717947006226</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.2947781085968</v>
+        <v>2.29477834701538</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.2947781085968</v>
+        <v>2.29477834701538</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.28717970848083</v>
+        <v>2.28717947006226</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.28717970848083</v>
+        <v>2.28717947006226</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.28717970848083</v>
+        <v>2.28717947006226</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.28717970848083</v>
+        <v>2.28717947006226</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.53793358802795</v>
+        <v>2.53793334960938</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.50753903388977</v>
+        <v>2.50753879547119</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.50753903388977</v>
+        <v>2.50753879547119</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.48474335670471</v>
+        <v>2.48474311828613</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.24918651580811</v>
+        <v>2.24918675422668</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.01363015174866</v>
+        <v>2.01362991333008</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.02882742881775</v>
+        <v>2.02882719039917</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.37076377868652</v>
+        <v>2.3707640171051</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.32517266273499</v>
+        <v>2.32517242431641</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.27958106994629</v>
+        <v>2.27958083152771</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.2947781085968</v>
+        <v>2.29477834701538</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.3614399433136</v>
+        <v>2.36143970489502</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.30578327178955</v>
+        <v>2.30578351020813</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.2819299697876</v>
+        <v>2.28193020820618</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.32963609695435</v>
+        <v>2.32963633537292</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.29783225059509</v>
+        <v>2.29783201217651</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.31373429298401</v>
+        <v>2.31373405456543</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.30578327178955</v>
+        <v>2.30578351020813</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.3614399433136</v>
+        <v>2.36143970489502</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.30578327178955</v>
+        <v>2.30578351020813</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.28988122940063</v>
+        <v>2.28988099098206</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.28988122940063</v>
+        <v>2.28988099098206</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.25012636184692</v>
+        <v>2.25012612342834</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.25012636184692</v>
+        <v>2.25012612342834</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.2580771446228</v>
+        <v>2.25807738304138</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.28988122940063</v>
+        <v>2.28988099098206</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.28988122940063</v>
+        <v>2.28988099098206</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.30578327178955</v>
+        <v>2.30578351020813</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.30578327178955</v>
+        <v>2.30578351020813</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.32963609695435</v>
+        <v>2.32963633537292</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.31373429298401</v>
+        <v>2.31373405456543</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.3375871181488</v>
+        <v>2.33758687973022</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.31373429298401</v>
+        <v>2.31373405456543</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.29783225059509</v>
+        <v>2.29783201217651</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.28988122940063</v>
+        <v>2.28988099098206</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.2819299697876</v>
+        <v>2.28193020820618</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.2819299697876</v>
+        <v>2.28193020820618</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.31373429298401</v>
+        <v>2.31373405456543</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.31373429298401</v>
+        <v>2.31373405456543</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.29783225059509</v>
+        <v>2.29783201217651</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.28988122940063</v>
+        <v>2.28988099098206</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.2580771446228</v>
+        <v>2.25807738304138</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.25012636184692</v>
+        <v>2.25012612342834</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.2580771446228</v>
+        <v>2.25807738304138</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.27397918701172</v>
+        <v>2.27397894859314</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.50455784797668</v>
+        <v>2.50455760955811</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.50455784797668</v>
+        <v>2.50455760955811</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.50455784797668</v>
+        <v>2.50455760955811</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.63972401618958</v>
+        <v>2.63972425460815</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.67947912216187</v>
+        <v>2.67947888374329</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.63972401618958</v>
+        <v>2.63972425460815</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.61587119102478</v>
+        <v>2.61587142944336</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.59996938705444</v>
+        <v>2.59996914863586</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.64767503738403</v>
+        <v>2.64767479896545</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.67152810096741</v>
+        <v>2.67152786254883</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.74308681488037</v>
+        <v>2.74308657646179</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.68743014335632</v>
+        <v>2.6874303817749</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.64767503738403</v>
+        <v>2.64767479896545</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.64767503738403</v>
+        <v>2.64767479896545</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.67947912216187</v>
+        <v>2.67947888374329</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.68743014335632</v>
+        <v>2.6874303817749</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65562605857849</v>
+        <v>2.65562582015991</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.69538116455078</v>
+        <v>2.6953809261322</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.75898885726929</v>
+        <v>2.75898909568787</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.76693987846375</v>
+        <v>2.76693964004517</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.79079270362854</v>
+        <v>2.79079246520996</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.90210628509521</v>
+        <v>2.90210652351379</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.65562605857849</v>
+        <v>2.65562582015991</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.68743014335632</v>
+        <v>2.6874303817749</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.67947912216187</v>
+        <v>2.67947888374329</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.66357707977295</v>
+        <v>2.66357731819153</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.74308681488037</v>
+        <v>2.74308657646179</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.67947912216187</v>
+        <v>2.67947888374329</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.65562605857849</v>
+        <v>2.65562582015991</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.62382221221924</v>
+        <v>2.62382197380066</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.63972401618958</v>
+        <v>2.63972425460815</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.66357707977295</v>
+        <v>2.66357731819153</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.66357707977295</v>
+        <v>2.66357731819153</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.65562605857849</v>
+        <v>2.65562582015991</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.6317732334137</v>
+        <v>2.63177299499512</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.63972401618958</v>
+        <v>2.63972425460815</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.66357707977295</v>
+        <v>2.66357731819153</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.6317732334137</v>
+        <v>2.63177299499512</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.6317732334137</v>
+        <v>2.63177299499512</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.64767503738403</v>
+        <v>2.64767479896545</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.67152810096741</v>
+        <v>2.67152786254883</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.63972401618958</v>
+        <v>2.63972425460815</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.71128296852112</v>
+        <v>2.7112832069397</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.73513579368591</v>
+        <v>2.73513603210449</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.74308681488037</v>
+        <v>2.74308657646179</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.71923398971558</v>
+        <v>2.719233751297</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.71923398971558</v>
+        <v>2.719233751297</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.66357707977295</v>
+        <v>2.66357731819153</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.71128296852112</v>
+        <v>2.7112832069397</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.71128296852112</v>
+        <v>2.7112832069397</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.71128296852112</v>
+        <v>2.7112832069397</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>18.5599994659424</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>74264</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>18.8600006103516</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>18.8600006103516</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>18.5799999237061</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>18.5799999237061</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>16.9599990844727</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>17.2600002288818</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>123005</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>17.0400009155273</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>17.2600002288818</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>17.2600002288818</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>17.1200008392334</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>81639</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>16.9400005340576</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>16.2600002288818</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>16.7600002288818</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>16.7600002288818</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>16.5400009155273</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>103549</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>16.0200004577637</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>16.3999996185303</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>16.4799995422363</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>67064</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>16.9200000762939</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>16.2800006866455</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>52845</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>16.7800006866455</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>16.3799991607666</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>16.3799991607666</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>16.6200008392334</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BDB.MI.xlsx
+++ b/data/BDB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73344719409943</v>
+        <v>1.73344731330872</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.70982003211975</v>
+        <v>1.70982015132904</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7110641002655</v>
+        <v>1.71106398105621</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71355104446411</v>
+        <v>1.71355080604553</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65634965896606</v>
+        <v>1.65634953975677</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5792521238327</v>
+        <v>1.57925248146057</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52329480648041</v>
+        <v>1.52329456806183</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G12" t="n">
-        <v>1.42008376121521</v>
+        <v>1.42008352279663</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43749272823334</v>
+        <v>1.43749260902405</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2994636297226</v>
+        <v>1.29946339130402</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G15" t="n">
-        <v>1.35542142391205</v>
+        <v>1.35542130470276</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41759657859802</v>
+        <v>1.41759645938873</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46111917495728</v>
+        <v>1.46111929416656</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>1.53075563907623</v>
+        <v>1.53075551986694</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45490181446075</v>
+        <v>1.45490169525146</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G22" t="n">
-        <v>1.50837254524231</v>
+        <v>1.5083726644516</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>1.49220705032349</v>
+        <v>1.49220681190491</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>1.43624913692474</v>
+        <v>1.43624925613403</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G25" t="n">
-        <v>1.41759657859802</v>
+        <v>1.41759645938873</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>1.34920394420624</v>
+        <v>1.34920382499695</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>1.46858024597168</v>
+        <v>1.46858048439026</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.39272618293762</v>
+        <v>1.39272654056549</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>1.41137886047363</v>
+        <v>1.41137909889221</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>1.48598957061768</v>
+        <v>1.4859893321991</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G33" t="n">
-        <v>1.48598957061768</v>
+        <v>1.4859893321991</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G35" t="n">
-        <v>1.52826857566833</v>
+        <v>1.52826881408691</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.5170773267746</v>
+        <v>1.51707720756531</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>1.52329480648041</v>
+        <v>1.52329456806183</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G40" t="n">
-        <v>1.48101544380188</v>
+        <v>1.48101532459259</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G41" t="n">
-        <v>1.52080762386322</v>
+        <v>1.52080774307251</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G43" t="n">
-        <v>1.52826857566833</v>
+        <v>1.52826881408691</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>1.52329480648041</v>
+        <v>1.52329456806183</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>1.49220705032349</v>
+        <v>1.49220681190491</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G47" t="n">
-        <v>1.47106719017029</v>
+        <v>1.47106754779816</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G48" t="n">
-        <v>1.44992768764496</v>
+        <v>1.44992792606354</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G49" t="n">
-        <v>1.46111917495728</v>
+        <v>1.46111929416656</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G50" t="n">
-        <v>1.49593722820282</v>
+        <v>1.49593734741211</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G53" t="n">
-        <v>1.52329480648041</v>
+        <v>1.52329456806183</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G54" t="n">
-        <v>1.53821682929993</v>
+        <v>1.53821671009064</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G55" t="n">
-        <v>1.52329480648041</v>
+        <v>1.52329456806183</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G56" t="n">
-        <v>1.50961589813232</v>
+        <v>1.50961601734161</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>1.53821682929993</v>
+        <v>1.53821671009064</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G58" t="n">
-        <v>1.54319083690643</v>
+        <v>1.54319071769714</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G62" t="n">
-        <v>1.52826857566833</v>
+        <v>1.52826881408691</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G63" t="n">
-        <v>1.52080762386322</v>
+        <v>1.52080774307251</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G64" t="n">
-        <v>1.48971962928772</v>
+        <v>1.4897198677063</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G66" t="n">
-        <v>1.3852653503418</v>
+        <v>1.38526523113251</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>1.38029158115387</v>
+        <v>1.38029170036316</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G68" t="n">
-        <v>1.48474609851837</v>
+        <v>1.48474586009979</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>1.53821682929993</v>
+        <v>1.53821671009064</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G70" t="n">
-        <v>1.55189514160156</v>
+        <v>1.55189526081085</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G72" t="n">
-        <v>1.54319083690643</v>
+        <v>1.54319071769714</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G73" t="n">
-        <v>1.56184315681458</v>
+        <v>1.56184303760529</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>1.56681716442108</v>
+        <v>1.56681728363037</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1.60837781429291</v>
+        <v>1.60837769508362</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G77" t="n">
-        <v>1.56334316730499</v>
+        <v>1.5633430480957</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G78" t="n">
-        <v>1.58007037639618</v>
+        <v>1.58007049560547</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G79" t="n">
-        <v>1.56334316730499</v>
+        <v>1.5633430480957</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G81" t="n">
-        <v>1.59808421134949</v>
+        <v>1.5980840921402</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G82" t="n">
-        <v>1.58779060840607</v>
+        <v>1.58779036998749</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G84" t="n">
-        <v>1.58393049240112</v>
+        <v>1.58393037319183</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G85" t="n">
-        <v>1.58135688304901</v>
+        <v>1.5813570022583</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G86" t="n">
-        <v>1.56076979637146</v>
+        <v>1.56076991558075</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.56977665424347</v>
+        <v>1.56977677345276</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G90" t="n">
-        <v>1.53374910354614</v>
+        <v>1.53374922275543</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G93" t="n">
-        <v>1.55304956436157</v>
+        <v>1.55304944515228</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G101" t="n">
-        <v>1.40893888473511</v>
+        <v>1.40893876552582</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G104" t="n">
-        <v>1.37419784069061</v>
+        <v>1.3741979598999</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G105" t="n">
-        <v>1.37677121162415</v>
+        <v>1.37677145004272</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G106" t="n">
-        <v>1.35875761508942</v>
+        <v>1.35875749588013</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.31243634223938</v>
+        <v>1.31243622303009</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>1.338170170784</v>
+        <v>1.33817040920258</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G110" t="n">
-        <v>1.34074366092682</v>
+        <v>1.34074378013611</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G111" t="n">
-        <v>1.33173644542694</v>
+        <v>1.33173668384552</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G112" t="n">
-        <v>1.29056227207184</v>
+        <v>1.29056215286255</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G113" t="n">
-        <v>1.32144331932068</v>
+        <v>1.32144296169281</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G116" t="n">
-        <v>1.18376624584198</v>
+        <v>1.1837660074234</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G117" t="n">
-        <v>1.11299753189087</v>
+        <v>1.11299741268158</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G118" t="n">
-        <v>1.03000509738922</v>
+        <v>1.03000521659851</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G119" t="n">
-        <v>1.10785055160522</v>
+        <v>1.10785067081451</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>1.16446542739868</v>
+        <v>1.16446554660797</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>1.16446542739868</v>
+        <v>1.16446554660797</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G125" t="n">
-        <v>1.0615291595459</v>
+        <v>1.06152927875519</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G126" t="n">
-        <v>1.06538939476013</v>
+        <v>1.06538951396942</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G127" t="n">
-        <v>1.0615291595459</v>
+        <v>1.06152927875519</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G128" t="n">
-        <v>1.09048008918762</v>
+        <v>1.09048020839691</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G129" t="n">
-        <v>1.09434020519257</v>
+        <v>1.09434008598328</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.64300000667572</v>
       </c>
       <c r="G130" t="n">
-        <v>1.05702579021454</v>
+        <v>1.05702590942383</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G131" t="n">
-        <v>1.04673218727112</v>
+        <v>1.04673230648041</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G132" t="n">
-        <v>1.02936172485352</v>
+        <v>1.02936196327209</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.04287219047546</v>
+        <v>1.04287207126617</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G136" t="n">
-        <v>1.07439625263214</v>
+        <v>1.07439637184143</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G137" t="n">
-        <v>1.07439625263214</v>
+        <v>1.07439637184143</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G139" t="n">
-        <v>1.10978078842163</v>
+        <v>1.10978066921234</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G140" t="n">
-        <v>1.10978078842163</v>
+        <v>1.10978066921234</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G144" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G145" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G147" t="n">
-        <v>1.09562695026398</v>
+        <v>1.09562683105469</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.0969135761261</v>
+        <v>1.09691369533539</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G150" t="n">
-        <v>1.09562695026398</v>
+        <v>1.09562683105469</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G155" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.11299753189087</v>
+        <v>1.11299741268158</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G159" t="n">
-        <v>1.13358461856842</v>
+        <v>1.13358449935913</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G161" t="n">
-        <v>1.11428427696228</v>
+        <v>1.11428415775299</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G162" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G163" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.12522113323212</v>
+        <v>1.12522125244141</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G165" t="n">
-        <v>1.14902496337891</v>
+        <v>1.14902520179749</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G167" t="n">
-        <v>1.12843799591064</v>
+        <v>1.12843763828278</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.75</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12586450576782</v>
+        <v>1.12586462497711</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.11492764949799</v>
+        <v>1.1149275302887</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G171" t="n">
-        <v>1.11428427696228</v>
+        <v>1.11428415775299</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>1.11299753189087</v>
+        <v>1.11299741268158</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G173" t="n">
-        <v>1.11299753189087</v>
+        <v>1.11299741268158</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G177" t="n">
-        <v>1.14194810390472</v>
+        <v>1.14194822311401</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15803205966949</v>
+        <v>1.15803194046021</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G179" t="n">
-        <v>1.13358461856842</v>
+        <v>1.13358449935913</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.75</v>
       </c>
       <c r="G180" t="n">
-        <v>1.12586450576782</v>
+        <v>1.12586462497711</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G181" t="n">
-        <v>1.14194810390472</v>
+        <v>1.14194822311401</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G183" t="n">
-        <v>1.18376624584198</v>
+        <v>1.1837660074234</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G184" t="n">
-        <v>1.20049321651459</v>
+        <v>1.2004930973053</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G185" t="n">
-        <v>1.20306658744812</v>
+        <v>1.20306646823883</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G186" t="n">
-        <v>1.17733263969421</v>
+        <v>1.17733228206635</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G187" t="n">
-        <v>1.17733263969421</v>
+        <v>1.17733228206635</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G188" t="n">
-        <v>1.18119251728058</v>
+        <v>1.18119275569916</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G189" t="n">
-        <v>1.19920647144318</v>
+        <v>1.19920635223389</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>1.16446542739868</v>
+        <v>1.16446554660797</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15095520019531</v>
+        <v>1.15095508098602</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>1.15095520019531</v>
+        <v>1.15095508098602</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.13873147964478</v>
+        <v>1.13873136043549</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G194" t="n">
-        <v>1.1322979927063</v>
+        <v>1.13229787349701</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G195" t="n">
-        <v>1.13937473297119</v>
+        <v>1.13937485218048</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G196" t="n">
-        <v>1.11557078361511</v>
+        <v>1.11557066440582</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G197" t="n">
-        <v>1.11557078361511</v>
+        <v>1.11557066440582</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G202" t="n">
-        <v>1.07568323612213</v>
+        <v>1.07568311691284</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G205" t="n">
-        <v>1.11042380332947</v>
+        <v>1.11042404174805</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G206" t="n">
-        <v>1.11042380332947</v>
+        <v>1.11042404174805</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10656404495239</v>
+        <v>1.1065639257431</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G209" t="n">
-        <v>1.13422811031342</v>
+        <v>1.13422787189484</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G211" t="n">
-        <v>1.09562695026398</v>
+        <v>1.09562683105469</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G212" t="n">
-        <v>1.08983683586121</v>
+        <v>1.08983671665192</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G213" t="n">
-        <v>1.10785055160522</v>
+        <v>1.10785067081451</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G214" t="n">
-        <v>1.08661997318268</v>
+        <v>1.08661985397339</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G215" t="n">
-        <v>1.08211660385132</v>
+        <v>1.08211648464203</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G216" t="n">
-        <v>1.0615291595459</v>
+        <v>1.06152927875519</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G217" t="n">
-        <v>1.05509567260742</v>
+        <v>1.05509579181671</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>1.03901183605194</v>
+        <v>1.03901195526123</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G220" t="n">
-        <v>1.06796288490295</v>
+        <v>1.06796276569366</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G221" t="n">
-        <v>1.03000509738922</v>
+        <v>1.03000521659851</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G222" t="n">
-        <v>1.0615291595459</v>
+        <v>1.06152927875519</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G224" t="n">
-        <v>1.05509567260742</v>
+        <v>1.05509579181671</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>1.03257846832275</v>
+        <v>1.03257858753204</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G226" t="n">
-        <v>1.03579533100128</v>
+        <v>1.03579521179199</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G227" t="n">
-        <v>1.01392149925232</v>
+        <v>1.01392114162445</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>1.01199126243591</v>
+        <v>1.0119913816452</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G231" t="n">
-        <v>0.992690920829773</v>
+        <v>0.992690563201904</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>0.990760743618011</v>
+        <v>0.990760684013367</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G234" t="n">
-        <v>1.0023410320282</v>
+        <v>1.00234091281891</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G235" t="n">
-        <v>1.00555765628815</v>
+        <v>1.00555777549744</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G236" t="n">
-        <v>0.985613822937012</v>
+        <v>0.985614001750946</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>1.00362765789032</v>
+        <v>1.00362777709961</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G239" t="n">
-        <v>1.00105440616608</v>
+        <v>1.0010541677475</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.58399999141693</v>
       </c>
       <c r="G240" t="n">
-        <v>1.01906800270081</v>
+        <v>1.0190681219101</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G241" t="n">
-        <v>1.03579533100128</v>
+        <v>1.03579521179199</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G245" t="n">
-        <v>1.10849404335022</v>
+        <v>1.10849392414093</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.13873147964478</v>
+        <v>1.13873136043549</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>1.15159833431244</v>
+        <v>1.15159845352173</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>1.15159833431244</v>
+        <v>1.15159845352173</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G251" t="n">
-        <v>1.18698287010193</v>
+        <v>1.18698275089264</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G252" t="n">
-        <v>1.17733263969421</v>
+        <v>1.17733228206635</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G253" t="n">
-        <v>1.20564007759094</v>
+        <v>1.20563995838165</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26096832752228</v>
+        <v>1.26096820831299</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G255" t="n">
-        <v>1.24938786029816</v>
+        <v>1.24938797950745</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G256" t="n">
-        <v>1.25517785549164</v>
+        <v>1.25517797470093</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26482820510864</v>
+        <v>1.26482832431793</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G258" t="n">
-        <v>1.3240168094635</v>
+        <v>1.32401669025421</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>1.49900782108307</v>
+        <v>1.49900794029236</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>1.43467283248901</v>
+        <v>1.43467307090759</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G264" t="n">
-        <v>1.43595957756042</v>
+        <v>1.43595969676971</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G265" t="n">
-        <v>1.43724656105042</v>
+        <v>1.43724644184113</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>1.44110643863678</v>
+        <v>1.44110655784607</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>1.44110643863678</v>
+        <v>1.44110655784607</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G270" t="n">
-        <v>1.44110643863678</v>
+        <v>1.44110655784607</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.25</v>
       </c>
       <c r="G272" t="n">
-        <v>1.44754004478455</v>
+        <v>1.44753992557526</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G273" t="n">
-        <v>1.43724656105042</v>
+        <v>1.43724644184113</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G275" t="n">
-        <v>1.43595957756042</v>
+        <v>1.43595969676971</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G277" t="n">
-        <v>1.45268678665161</v>
+        <v>1.45268666744232</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44110643863678</v>
+        <v>1.44110655784607</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G281" t="n">
-        <v>1.46555399894714</v>
+        <v>1.46555387973785</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>1.50801515579224</v>
+        <v>1.50801503658295</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G285" t="n">
-        <v>1.56334316730499</v>
+        <v>1.5633430480957</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G287" t="n">
-        <v>1.52602875232697</v>
+        <v>1.52602899074554</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>1.49900782108307</v>
+        <v>1.49900794029236</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G291" t="n">
-        <v>1.47970759868622</v>
+        <v>1.47970736026764</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>1.47970759868622</v>
+        <v>1.47970736026764</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>1.47970759868622</v>
+        <v>1.47970736026764</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G295" t="n">
-        <v>1.45783376693726</v>
+        <v>1.45783364772797</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G297" t="n">
-        <v>1.4436799287796</v>
+        <v>1.44367969036102</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.44110643863678</v>
+        <v>1.44110655784607</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G301" t="n">
-        <v>1.40893888473511</v>
+        <v>1.40893876552582</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G302" t="n">
-        <v>1.40507900714874</v>
+        <v>1.40507876873016</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G305" t="n">
-        <v>1.37805807590485</v>
+        <v>1.37805795669556</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>1.37677121162415</v>
+        <v>1.37677145004272</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G308" t="n">
-        <v>1.38963842391968</v>
+        <v>1.38963830471039</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37162458896637</v>
+        <v>1.37162446975708</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G311" t="n">
-        <v>1.41151249408722</v>
+        <v>1.41151225566864</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G313" t="n">
-        <v>1.40250551700592</v>
+        <v>1.40250539779663</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G315" t="n">
-        <v>1.42051923274994</v>
+        <v>1.42051935195923</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>1.45654702186584</v>
+        <v>1.45654690265656</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G317" t="n">
-        <v>1.47070062160492</v>
+        <v>1.47070050239563</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G318" t="n">
-        <v>1.49772131443024</v>
+        <v>1.49772119522095</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G319" t="n">
-        <v>1.49128782749176</v>
+        <v>1.49128794670105</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G320" t="n">
-        <v>1.48742771148682</v>
+        <v>1.48742783069611</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G321" t="n">
-        <v>1.54275572299957</v>
+        <v>1.54275584220886</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G322" t="n">
-        <v>1.54275572299957</v>
+        <v>1.54275584220886</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G323" t="n">
-        <v>1.54918920993805</v>
+        <v>1.54918968677521</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>1.54918920993805</v>
+        <v>1.54918968677521</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G326" t="n">
-        <v>1.65341246128082</v>
+        <v>1.65341222286224</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G327" t="n">
-        <v>1.66627931594849</v>
+        <v>1.66627907752991</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G328" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>1.57489812374115</v>
+        <v>1.57489800453186</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G331" t="n">
-        <v>1.59485042095184</v>
+        <v>1.59485018253326</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G333" t="n">
-        <v>1.58819949626923</v>
+        <v>1.58819961547852</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G335" t="n">
-        <v>1.55095541477203</v>
+        <v>1.55095529556274</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G336" t="n">
-        <v>1.6281042098999</v>
+        <v>1.62810397148132</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G337" t="n">
-        <v>1.66534817218781</v>
+        <v>1.66534829139709</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.5</v>
       </c>
       <c r="G338" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G339" t="n">
-        <v>1.66534817218781</v>
+        <v>1.66534829139709</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66933882236481</v>
+        <v>1.6693389415741</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.5</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G342" t="n">
-        <v>1.62677383422852</v>
+        <v>1.62677395343781</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G343" t="n">
-        <v>1.64273583889008</v>
+        <v>1.64273571968079</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G344" t="n">
-        <v>1.6281042098999</v>
+        <v>1.62810397148132</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G346" t="n">
-        <v>1.62677383422852</v>
+        <v>1.62677395343781</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G348" t="n">
-        <v>1.60150110721588</v>
+        <v>1.60150122642517</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>1.62943410873413</v>
+        <v>1.62943422794342</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.5</v>
       </c>
       <c r="G351" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.68264007568359</v>
+        <v>1.68264019489288</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G355" t="n">
-        <v>1.70392286777496</v>
+        <v>1.70392274856567</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G356" t="n">
-        <v>1.70392286777496</v>
+        <v>1.70392274856567</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G358" t="n">
-        <v>1.67998003959656</v>
+        <v>1.67997980117798</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G359" t="n">
-        <v>1.73584651947021</v>
+        <v>1.73584628105164</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G360" t="n">
-        <v>1.68397033214569</v>
+        <v>1.68397009372711</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69594156742096</v>
+        <v>1.69594180583954</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68264007568359</v>
+        <v>1.68264019489288</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G363" t="n">
-        <v>1.65736734867096</v>
+        <v>1.65736758708954</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G364" t="n">
-        <v>1.6866307258606</v>
+        <v>1.68663048744202</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G367" t="n">
-        <v>1.69461166858673</v>
+        <v>1.69461154937744</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>1.68264007568359</v>
+        <v>1.68264019489288</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G369" t="n">
-        <v>1.69461166858673</v>
+        <v>1.69461154937744</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G370" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70126247406006</v>
+        <v>1.70126259326935</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G372" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G373" t="n">
-        <v>1.6666784286499</v>
+        <v>1.66667854785919</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.5</v>
       </c>
       <c r="G374" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G376" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259261131287</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G379" t="n">
-        <v>1.71323359012604</v>
+        <v>1.71323382854462</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G380" t="n">
-        <v>1.71589410305023</v>
+        <v>1.71589398384094</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259261131287</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G382" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259261131287</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259261131287</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259261131287</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G385" t="n">
-        <v>1.66933882236481</v>
+        <v>1.6693389415741</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G386" t="n">
-        <v>1.68530058860779</v>
+        <v>1.68530023097992</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G387" t="n">
-        <v>1.67332923412323</v>
+        <v>1.67332911491394</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G388" t="n">
-        <v>1.67332923412323</v>
+        <v>1.67332911491394</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G389" t="n">
-        <v>1.65470683574677</v>
+        <v>1.65470707416534</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>1.69594156742096</v>
+        <v>1.69594180583954</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G391" t="n">
-        <v>1.69594156742096</v>
+        <v>1.69594180583954</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.5</v>
       </c>
       <c r="G392" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G393" t="n">
-        <v>1.69328153133392</v>
+        <v>1.69328165054321</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G394" t="n">
-        <v>1.68397033214569</v>
+        <v>1.68397009372711</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G395" t="n">
-        <v>1.69195127487183</v>
+        <v>1.69195139408112</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.71057343482971</v>
+        <v>1.71057367324829</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G398" t="n">
-        <v>1.70126247406006</v>
+        <v>1.70126259326935</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G399" t="n">
-        <v>1.70392286777496</v>
+        <v>1.70392274856567</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>1.70259249210358</v>
+        <v>1.70259261131287</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>1.71589410305023</v>
+        <v>1.71589398384094</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.5</v>
       </c>
       <c r="G404" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G405" t="n">
-        <v>1.65736734867096</v>
+        <v>1.65736758708954</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G406" t="n">
-        <v>1.664018034935</v>
+        <v>1.66401827335358</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G409" t="n">
-        <v>1.67864954471588</v>
+        <v>1.67864978313446</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G410" t="n">
-        <v>1.69993221759796</v>
+        <v>1.69993233680725</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G411" t="n">
-        <v>1.70126247406006</v>
+        <v>1.70126259326935</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68264007568359</v>
+        <v>1.68264019489288</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G413" t="n">
-        <v>1.664018034935</v>
+        <v>1.66401827335358</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G414" t="n">
-        <v>1.64007568359375</v>
+        <v>1.64007532596588</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G415" t="n">
-        <v>1.64007568359375</v>
+        <v>1.64007532596588</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G416" t="n">
-        <v>1.65470683574677</v>
+        <v>1.65470707416534</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G417" t="n">
-        <v>1.66534817218781</v>
+        <v>1.66534829139709</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G418" t="n">
-        <v>1.65204656124115</v>
+        <v>1.65204679965973</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G419" t="n">
-        <v>1.67199873924255</v>
+        <v>1.67199885845184</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.65204656124115</v>
+        <v>1.65204679965973</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>1.68397033214569</v>
+        <v>1.68397009372711</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G422" t="n">
-        <v>1.67998003959656</v>
+        <v>1.67997980117798</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1.66268801689148</v>
+        <v>1.66268789768219</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>1.66933882236481</v>
+        <v>1.6693389415741</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G427" t="n">
-        <v>1.63342475891113</v>
+        <v>1.63342487812042</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G429" t="n">
-        <v>1.61480259895325</v>
+        <v>1.61480271816254</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G430" t="n">
-        <v>1.6054915189743</v>
+        <v>1.60549139976501</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G431" t="n">
-        <v>1.55893635749817</v>
+        <v>1.55893647670746</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G432" t="n">
-        <v>1.56824731826782</v>
+        <v>1.56824743747711</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G434" t="n">
-        <v>1.54430460929871</v>
+        <v>1.544304728508</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G436" t="n">
-        <v>1.52967274188995</v>
+        <v>1.52967286109924</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G438" t="n">
-        <v>1.51504135131836</v>
+        <v>1.51504111289978</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>1.52302229404449</v>
+        <v>1.52302217483521</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G441" t="n">
-        <v>1.54164433479309</v>
+        <v>1.5416442155838</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>1.52302229404449</v>
+        <v>1.52302217483521</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G447" t="n">
-        <v>1.63475477695465</v>
+        <v>1.63475501537323</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G449" t="n">
-        <v>1.68131029605865</v>
+        <v>1.68131005764008</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G450" t="n">
-        <v>1.65603733062744</v>
+        <v>1.65603744983673</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G451" t="n">
-        <v>1.66002762317657</v>
+        <v>1.66002786159515</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>1.66933882236481</v>
+        <v>1.6693389415741</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G453" t="n">
-        <v>1.67332923412323</v>
+        <v>1.67332911491394</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G454" t="n">
-        <v>1.68264007568359</v>
+        <v>1.68264019489288</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>1.67598962783813</v>
+        <v>1.67598938941956</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G456" t="n">
-        <v>1.68397033214569</v>
+        <v>1.68397009372711</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G457" t="n">
-        <v>1.63874518871307</v>
+        <v>1.63874506950378</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G458" t="n">
-        <v>1.6054915189743</v>
+        <v>1.60549139976501</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G460" t="n">
-        <v>1.58819949626923</v>
+        <v>1.58819961547852</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>1.57622814178467</v>
+        <v>1.57622826099396</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G462" t="n">
-        <v>1.55627608299255</v>
+        <v>1.55627572536469</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G463" t="n">
-        <v>1.56824731826782</v>
+        <v>1.56824743747711</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>1.60948204994202</v>
+        <v>1.60948193073273</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58952963352203</v>
+        <v>1.58952975273132</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G467" t="n">
-        <v>1.62677383422852</v>
+        <v>1.62677395343781</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G468" t="n">
-        <v>1.61746287345886</v>
+        <v>1.61746275424957</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G469" t="n">
-        <v>1.6281042098999</v>
+        <v>1.62810397148132</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>1.62943410873413</v>
+        <v>1.62943422794342</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64273583889008</v>
+        <v>1.64273571968079</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G473" t="n">
-        <v>1.65337693691254</v>
+        <v>1.65337705612183</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G474" t="n">
-        <v>1.64273583889008</v>
+        <v>1.64273571968079</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.64938628673553</v>
+        <v>1.6493866443634</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G476" t="n">
-        <v>1.58952963352203</v>
+        <v>1.58952975273132</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>1.58952963352203</v>
+        <v>1.58952975273132</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.57755839824677</v>
+        <v>1.57755851745605</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G484" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G485" t="n">
-        <v>1.5256826877594</v>
+        <v>1.52568244934082</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G489" t="n">
-        <v>1.57356786727905</v>
+        <v>1.57356798648834</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G490" t="n">
-        <v>1.53366339206696</v>
+        <v>1.53366327285767</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>1.59618043899536</v>
+        <v>1.59618055820465</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>1.57622814178467</v>
+        <v>1.57622826099396</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G495" t="n">
-        <v>1.57622814178467</v>
+        <v>1.57622826099396</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>1.57622814178467</v>
+        <v>1.57622826099396</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G501" t="n">
-        <v>1.51238119602203</v>
+        <v>1.51238095760345</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G502" t="n">
-        <v>1.51371121406555</v>
+        <v>1.51371145248413</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G504" t="n">
-        <v>1.5256826877594</v>
+        <v>1.52568244934082</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.50972056388855</v>
+        <v>1.50972080230713</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G508" t="n">
-        <v>1.51371121406555</v>
+        <v>1.51371145248413</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G509" t="n">
-        <v>1.51903164386749</v>
+        <v>1.51903176307678</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G510" t="n">
-        <v>1.49375879764557</v>
+        <v>1.49375891685486</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G511" t="n">
-        <v>1.52834260463715</v>
+        <v>1.52834296226501</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G512" t="n">
-        <v>1.49109876155853</v>
+        <v>1.49109888076782</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G514" t="n">
-        <v>1.50306987762451</v>
+        <v>1.5030699968338</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.50972056388855</v>
+        <v>1.50972080230713</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>1.50972056388855</v>
+        <v>1.50972080230713</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G519" t="n">
-        <v>1.50972056388855</v>
+        <v>1.50972080230713</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G522" t="n">
-        <v>1.55627608299255</v>
+        <v>1.55627572536469</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G525" t="n">
-        <v>1.52967274188995</v>
+        <v>1.52967286109924</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G526" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G527" t="n">
-        <v>1.52967274188995</v>
+        <v>1.52967286109924</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G528" t="n">
-        <v>1.53632390499115</v>
+        <v>1.53632378578186</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>1.52967274188995</v>
+        <v>1.52967286109924</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.57622814178467</v>
+        <v>1.57622826099396</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.55627608299255</v>
+        <v>1.55627572536469</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G532" t="n">
-        <v>1.55627608299255</v>
+        <v>1.55627572536469</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>1.50972056388855</v>
+        <v>1.50972080230713</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>1.44321322441101</v>
+        <v>1.44321310520172</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>1.42326104640961</v>
+        <v>1.42326092720032</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>1.42991185188293</v>
+        <v>1.42991173267365</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>1.44321322441101</v>
+        <v>1.44321310520172</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>1.46981608867645</v>
+        <v>1.46981620788574</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.46981608867645</v>
+        <v>1.46981620788574</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G546" t="n">
-        <v>1.44986379146576</v>
+        <v>1.44986391067505</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>1.44986379146576</v>
+        <v>1.44986391067505</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>1.44321322441101</v>
+        <v>1.44321310520172</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G552" t="n">
-        <v>1.37670576572418</v>
+        <v>1.3767055273056</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>1.41661024093628</v>
+        <v>1.41661012172699</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>1.40330862998962</v>
+        <v>1.40330839157104</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.39665770530701</v>
+        <v>1.39665794372559</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G556" t="n">
-        <v>1.40330862998962</v>
+        <v>1.40330839157104</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G557" t="n">
-        <v>1.40330862998962</v>
+        <v>1.40330839157104</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G558" t="n">
-        <v>1.40330862998962</v>
+        <v>1.40330839157104</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G560" t="n">
-        <v>1.47646713256836</v>
+        <v>1.47646701335907</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>1.46981608867645</v>
+        <v>1.46981620788574</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.47646713256836</v>
+        <v>1.47646701335907</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G568" t="n">
-        <v>1.44986379146576</v>
+        <v>1.44986391067505</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>1.42991185188293</v>
+        <v>1.42991173267365</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>1.44986379146576</v>
+        <v>1.44986391067505</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G577" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G580" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G582" t="n">
-        <v>1.53291296958923</v>
+        <v>1.53291285037994</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G584" t="n">
-        <v>1.56078398227692</v>
+        <v>1.5607842206955</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.58168745040894</v>
+        <v>1.58168756961823</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>1.60955858230591</v>
+        <v>1.6095587015152</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G589" t="n">
-        <v>1.64439737796783</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G590" t="n">
-        <v>1.64439737796783</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G593" t="n">
-        <v>1.64439737796783</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>1.66530084609985</v>
+        <v>1.66530096530914</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G598" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>1.64439737796783</v>
+        <v>1.64439749717712</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>1.66530084609985</v>
+        <v>1.66530096530914</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G604" t="n">
-        <v>1.65136516094208</v>
+        <v>1.65136528015137</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G605" t="n">
-        <v>1.63046193122864</v>
+        <v>1.63046181201935</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G606" t="n">
-        <v>1.60955858230591</v>
+        <v>1.6095587015152</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>1.55381631851196</v>
+        <v>1.55381643772125</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.55381631851196</v>
+        <v>1.55381643772125</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>1.55381631851196</v>
+        <v>1.55381643772125</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G614" t="n">
-        <v>1.38658952713013</v>
+        <v>1.38658940792084</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G615" t="n">
-        <v>1.40052497386932</v>
+        <v>1.40052485466003</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>1.40052497386932</v>
+        <v>1.40052485466003</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G619" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.43536388874054</v>
+        <v>1.43536400794983</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G625" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G628" t="n">
-        <v>1.43536388874054</v>
+        <v>1.43536400794983</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.53291296958923</v>
+        <v>1.53291285037994</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G648" t="n">
-        <v>1.53291296958923</v>
+        <v>1.53291285037994</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G658" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G663" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G664" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G665" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>1.49807405471802</v>
+        <v>1.49807393550873</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G672" t="n">
-        <v>1.45626711845398</v>
+        <v>1.45626735687256</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G676" t="n">
-        <v>1.45626711845398</v>
+        <v>1.45626735687256</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G677" t="n">
-        <v>1.45626711845398</v>
+        <v>1.45626735687256</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>1.43536388874054</v>
+        <v>1.43536400794983</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>1.41446042060852</v>
+        <v>1.41446053981781</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.40052497386932</v>
+        <v>1.40052485466003</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G682" t="n">
-        <v>1.42142832279205</v>
+        <v>1.42142820358276</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.41446042060852</v>
+        <v>1.41446053981781</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G685" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G686" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>1.42142832279205</v>
+        <v>1.42142820358276</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>1.43536388874054</v>
+        <v>1.43536400794983</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G695" t="n">
-        <v>1.44233179092407</v>
+        <v>1.44233155250549</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G696" t="n">
-        <v>1.46323490142822</v>
+        <v>1.46323502063751</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G699" t="n">
-        <v>1.51897728443146</v>
+        <v>1.51897740364075</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>1.43536388874054</v>
+        <v>1.43536400794983</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>1.42142832279205</v>
+        <v>1.42142820358276</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G704" t="n">
-        <v>1.43536388874054</v>
+        <v>1.43536400794983</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2</v>
       </c>
       <c r="G706" t="n">
-        <v>1.39355719089508</v>
+        <v>1.39355731010437</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G707" t="n">
-        <v>1.32387948036194</v>
+        <v>1.32387924194336</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G710" t="n">
-        <v>1.32387948036194</v>
+        <v>1.32387924194336</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G711" t="n">
-        <v>1.35523438453674</v>
+        <v>1.35523450374603</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G713" t="n">
-        <v>1.37265384197235</v>
+        <v>1.37265408039093</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.3482666015625</v>
+        <v>1.34826648235321</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G718" t="n">
-        <v>1.2820725440979</v>
+        <v>1.28207266330719</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G720" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G721" t="n">
-        <v>1.18452382087708</v>
+        <v>1.1845235824585</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G724" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G725" t="n">
-        <v>1.31691145896912</v>
+        <v>1.31691157817841</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G726" t="n">
-        <v>1.28904056549072</v>
+        <v>1.28904044628143</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G728" t="n">
-        <v>1.28904056549072</v>
+        <v>1.28904044628143</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G729" t="n">
-        <v>1.31691145896912</v>
+        <v>1.31691157817841</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30297601222992</v>
+        <v>1.30297589302063</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G732" t="n">
-        <v>1.31342756748199</v>
+        <v>1.31342768669128</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G733" t="n">
-        <v>1.30994391441345</v>
+        <v>1.30994379520416</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G734" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G737" t="n">
-        <v>1.22284638881683</v>
+        <v>1.22284626960754</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.18452382087708</v>
+        <v>1.1845235824585</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.75</v>
       </c>
       <c r="G739" t="n">
-        <v>1.21936273574829</v>
+        <v>1.21936249732971</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G740" t="n">
-        <v>1.22633028030396</v>
+        <v>1.22633039951324</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>1.21239471435547</v>
+        <v>1.21239483356476</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G742" t="n">
-        <v>1.26465344429016</v>
+        <v>1.26465308666229</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>1.24723374843597</v>
+        <v>1.24723362922668</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G745" t="n">
-        <v>1.21239471435547</v>
+        <v>1.21239483356476</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G747" t="n">
-        <v>1.27510488033295</v>
+        <v>1.27510499954224</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G750" t="n">
-        <v>1.22633028030396</v>
+        <v>1.22633039951324</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.75</v>
       </c>
       <c r="G752" t="n">
-        <v>1.21936273574829</v>
+        <v>1.21936249732971</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.23678195476532</v>
+        <v>1.2367821931839</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G758" t="n">
-        <v>1.2820725440979</v>
+        <v>1.28207266330719</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G761" t="n">
-        <v>1.17058789730072</v>
+        <v>1.17058801651001</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.18452382087708</v>
+        <v>1.1845235824585</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.75</v>
       </c>
       <c r="G767" t="n">
-        <v>1.21936273574829</v>
+        <v>1.21936249732971</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G768" t="n">
-        <v>1.20891094207764</v>
+        <v>1.20891106128693</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G769" t="n">
-        <v>1.22981417179108</v>
+        <v>1.22981429100037</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G770" t="n">
-        <v>1.22981417179108</v>
+        <v>1.22981429100037</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G771" t="n">
-        <v>1.23678195476532</v>
+        <v>1.2367821931839</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>1.24723374843597</v>
+        <v>1.24723362922668</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G773" t="n">
-        <v>1.18452382087708</v>
+        <v>1.1845235824585</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G774" t="n">
-        <v>1.22633028030396</v>
+        <v>1.22633039951324</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.23678195476532</v>
+        <v>1.2367821931839</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G778" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>1.24723374843597</v>
+        <v>1.24723362922668</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.24723374843597</v>
+        <v>1.24723362922668</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G785" t="n">
-        <v>1.26116919517517</v>
+        <v>1.26116931438446</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G789" t="n">
-        <v>1.27510488033295</v>
+        <v>1.27510499954224</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G790" t="n">
-        <v>1.2820725440979</v>
+        <v>1.28207266330719</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>1.24723374843597</v>
+        <v>1.24723362922668</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G792" t="n">
-        <v>1.2820725440979</v>
+        <v>1.28207266330719</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G793" t="n">
-        <v>1.2820725440979</v>
+        <v>1.28207266330719</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G794" t="n">
-        <v>1.32387948036194</v>
+        <v>1.32387924194336</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.30297601222992</v>
+        <v>1.30297589302063</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G797" t="n">
-        <v>1.28904056549072</v>
+        <v>1.28904044628143</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>1.32736313343048</v>
+        <v>1.32736325263977</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G799" t="n">
-        <v>1.31342756748199</v>
+        <v>1.31342768669128</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G800" t="n">
-        <v>1.32736313343048</v>
+        <v>1.32736325263977</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G801" t="n">
-        <v>1.31691145896912</v>
+        <v>1.31691157817841</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G802" t="n">
-        <v>1.31342756748199</v>
+        <v>1.31342768669128</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G804" t="n">
-        <v>1.32736313343048</v>
+        <v>1.32736325263977</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G806" t="n">
-        <v>1.35523438453674</v>
+        <v>1.35523450374603</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.3482666015625</v>
+        <v>1.34826648235321</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G812" t="n">
-        <v>1.36916995048523</v>
+        <v>1.36916983127594</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G813" t="n">
-        <v>1.35523438453674</v>
+        <v>1.35523450374603</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G815" t="n">
-        <v>1.37265384197235</v>
+        <v>1.37265408039093</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G816" t="n">
-        <v>1.37265384197235</v>
+        <v>1.37265408039093</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G819" t="n">
-        <v>1.38658952713013</v>
+        <v>1.38658940792084</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G820" t="n">
-        <v>1.40052497386932</v>
+        <v>1.40052485466003</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G821" t="n">
-        <v>1.37613785266876</v>
+        <v>1.37613773345947</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2</v>
       </c>
       <c r="G824" t="n">
-        <v>1.39355719089508</v>
+        <v>1.39355731010437</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G825" t="n">
-        <v>1.37265384197235</v>
+        <v>1.37265408039093</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G828" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G829" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G835" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G837" t="n">
-        <v>1.48432469367981</v>
+        <v>1.48432457447052</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>1.48432469367981</v>
+        <v>1.48432457447052</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>1.48432469367981</v>
+        <v>1.48432457447052</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>1.48432469367981</v>
+        <v>1.48432457447052</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G845" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2</v>
       </c>
       <c r="G849" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2</v>
       </c>
       <c r="G851" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G855" t="n">
-        <v>1.40428745746613</v>
+        <v>1.40428757667542</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G857" t="n">
-        <v>1.43339204788208</v>
+        <v>1.43339228630066</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G858" t="n">
-        <v>1.40792560577393</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G859" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G860" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38609719276428</v>
+        <v>1.38609731197357</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G864" t="n">
-        <v>1.36063098907471</v>
+        <v>1.36063075065613</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G866" t="n">
-        <v>1.36063098907471</v>
+        <v>1.36063075065613</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G867" t="n">
-        <v>1.37154507637024</v>
+        <v>1.37154531478882</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.33880257606506</v>
+        <v>1.33880281448364</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G869" t="n">
-        <v>1.34607887268066</v>
+        <v>1.34607875347137</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G870" t="n">
-        <v>1.37154507637024</v>
+        <v>1.37154531478882</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G871" t="n">
-        <v>1.3533548116684</v>
+        <v>1.35335493087769</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G872" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G874" t="n">
-        <v>1.38609719276428</v>
+        <v>1.38609731197357</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G875" t="n">
-        <v>1.41520178318024</v>
+        <v>1.41520190238953</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G876" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247772216797</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.43339204788208</v>
+        <v>1.43339228630066</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G880" t="n">
-        <v>1.40428745746613</v>
+        <v>1.40428757667542</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G882" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G883" t="n">
-        <v>1.43339204788208</v>
+        <v>1.43339228630066</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G885" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G886" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247772216797</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G888" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G889" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2</v>
       </c>
       <c r="G891" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2</v>
       </c>
       <c r="G892" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2</v>
       </c>
       <c r="G893" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2</v>
       </c>
       <c r="G896" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50615310668945</v>
+        <v>1.50615298748016</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50615310668945</v>
+        <v>1.50615298748016</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G910" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247772216797</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2</v>
       </c>
       <c r="G912" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G915" t="n">
-        <v>1.43339204788208</v>
+        <v>1.43339228630066</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2</v>
       </c>
       <c r="G916" t="n">
-        <v>1.45522022247314</v>
+        <v>1.45522034168243</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>1.43339204788208</v>
+        <v>1.43339228630066</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.40792560577393</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G921" t="n">
-        <v>1.40792560577393</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G923" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247772216797</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G924" t="n">
-        <v>1.38609719276428</v>
+        <v>1.38609731197357</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>1.37882137298584</v>
+        <v>1.37882125377655</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.38609719276428</v>
+        <v>1.38609731197357</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>1.40792560577393</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G930" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G932" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.37882137298584</v>
+        <v>1.37882125377655</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G936" t="n">
-        <v>1.40792560577393</v>
+        <v>1.40792548656464</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G937" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G938" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G939" t="n">
-        <v>1.38973546028137</v>
+        <v>1.38973534107208</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G940" t="n">
-        <v>1.38245940208435</v>
+        <v>1.38245928287506</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G941" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G949" t="n">
-        <v>1.40428745746613</v>
+        <v>1.40428757667542</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G950" t="n">
-        <v>1.38609719276428</v>
+        <v>1.38609731197357</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G951" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G952" t="n">
-        <v>1.40428745746613</v>
+        <v>1.40428757667542</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G954" t="n">
-        <v>1.40428745746613</v>
+        <v>1.40428757667542</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G956" t="n">
-        <v>1.41520178318024</v>
+        <v>1.41520190238953</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G957" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.41520178318024</v>
+        <v>1.41520190238953</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G959" t="n">
-        <v>1.40428745746613</v>
+        <v>1.40428757667542</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G960" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G961" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G963" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G964" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247772216797</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G965" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G971" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.50615310668945</v>
+        <v>1.50615298748016</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G976" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G980" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G982" t="n">
-        <v>1.56436192989349</v>
+        <v>1.5643618106842</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>1.59346640110016</v>
+        <v>1.59346628189087</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G990" t="n">
-        <v>1.59346640110016</v>
+        <v>1.59346628189087</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G991" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G993" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.76081657409668</v>
+        <v>1.76081681251526</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.8117493391037</v>
+        <v>1.81174921989441</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.77536880970001</v>
+        <v>1.77536904811859</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.82630169391632</v>
+        <v>1.82630157470703</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.81902527809143</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.8117493391037</v>
+        <v>1.81174921989441</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.84812986850739</v>
+        <v>1.8481297492981</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.90633845329285</v>
+        <v>1.90633869171143</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.91361474990845</v>
+        <v>1.91361486911774</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.88451027870178</v>
+        <v>1.88451015949249</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.90633845329285</v>
+        <v>1.90633869171143</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.97182333469391</v>
+        <v>1.97182369232178</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.97909951210022</v>
+        <v>1.9790997505188</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.98637580871582</v>
+        <v>1.98637568950653</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.03730845451355</v>
+        <v>2.03730869293213</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.07368898391724</v>
+        <v>2.07368874549866</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.0882408618927</v>
+        <v>2.08824110031128</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.13189768791199</v>
+        <v>2.13189792633057</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.13189768791199</v>
+        <v>2.13189792633057</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.13189768791199</v>
+        <v>2.13189792633057</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.12462162971497</v>
+        <v>2.12462186813354</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.13189768791199</v>
+        <v>2.13189792633057</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.16827821731567</v>
+        <v>2.16827845573425</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.27741980552673</v>
+        <v>2.27742004394531</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.29924845695496</v>
+        <v>2.2992479801178</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.29197239875793</v>
+        <v>2.29197216033936</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.29197239875793</v>
+        <v>2.29197216033936</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34290456771851</v>
+        <v>2.34290480613708</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.35018062591553</v>
+        <v>2.35018086433411</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.226487159729</v>
+        <v>2.22648692131042</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.14645028114319</v>
+        <v>2.14645004272461</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.03730845451355</v>
+        <v>2.03730869293213</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.00820422172546</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.00820422172546</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.93544328212738</v>
+        <v>1.9354430437088</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97909951210022</v>
+        <v>1.9790997505188</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.94999504089355</v>
+        <v>1.94999539852142</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.03003239631653</v>
+        <v>2.03003215789795</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.03003239631653</v>
+        <v>2.03003215789795</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.12462162971497</v>
+        <v>2.12462186813354</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.12462162971497</v>
+        <v>2.12462186813354</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.19738245010376</v>
+        <v>2.19738268852234</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.10279321670532</v>
+        <v>2.1027934551239</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97909951210022</v>
+        <v>1.9790997505188</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.93544328212738</v>
+        <v>1.9354430437088</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.89178621768951</v>
+        <v>1.89178609848022</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.91361474990845</v>
+        <v>1.91361486911774</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.99365174770355</v>
+        <v>1.99365198612213</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.89178621768951</v>
+        <v>1.89178609848022</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.89178621768951</v>
+        <v>1.89178609848022</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.89178621768951</v>
+        <v>1.89178609848022</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.86995816230774</v>
+        <v>1.86995804309845</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.90633845329285</v>
+        <v>1.90633869171143</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.84812986850739</v>
+        <v>1.8481297492981</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.85540556907654</v>
+        <v>1.85540568828583</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.5</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.81902527809143</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>2.5</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.81902527809143</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.84812986850739</v>
+        <v>1.8481297492981</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>2.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.81902527809143</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.6880556344986</v>
+        <v>1.68805551528931</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.73171210289001</v>
+        <v>1.73171234130859</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.75354063510895</v>
+        <v>1.75354027748108</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.84812986850739</v>
+        <v>1.8481297492981</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.81902527809143</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.75354063510895</v>
+        <v>1.75354027748108</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.73171210289001</v>
+        <v>1.73171234130859</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70260775089264</v>
+        <v>1.70260763168335</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.71715986728668</v>
+        <v>1.71715998649597</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.59346640110016</v>
+        <v>1.59346628189087</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.73171210289001</v>
+        <v>1.73171234130859</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.75354063510895</v>
+        <v>1.75354027748108</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.7244359254837</v>
+        <v>1.72443604469299</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69533181190491</v>
+        <v>1.69533145427704</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.62257063388824</v>
+        <v>1.62257075309753</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.70260775089264</v>
+        <v>1.70260763168335</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.73171210289001</v>
+        <v>1.73171234130859</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74626433849335</v>
+        <v>1.74626445770264</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.7244359254837</v>
+        <v>1.72443604469299</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.69533181190491</v>
+        <v>1.69533145427704</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.69533181190491</v>
+        <v>1.69533145427704</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.62984669208527</v>
+        <v>1.62984681129456</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.50615310668945</v>
+        <v>1.50615298748016</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.48432469367981</v>
+        <v>1.48432457447052</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.46249639987946</v>
+        <v>1.46249628067017</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.47704839706421</v>
+        <v>1.47704863548279</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.50615310668945</v>
+        <v>1.50615298748016</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53525733947754</v>
+        <v>1.53525745868683</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.42247784137726</v>
+        <v>1.42247772216797</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.4406681060791</v>
+        <v>1.44066798686981</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.41156375408173</v>
+        <v>1.41156387329102</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.38245940208435</v>
+        <v>1.38245928287506</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.4006495475769</v>
+        <v>1.40064966678619</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.3533548116684</v>
+        <v>1.35335493087769</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.42611598968506</v>
+        <v>1.42611587047577</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.70260775089264</v>
+        <v>1.70260763168335</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.73171210289001</v>
+        <v>1.73171234130859</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.7244359254837</v>
+        <v>1.72443604469299</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.77536880970001</v>
+        <v>1.77536904811859</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.76081657409668</v>
+        <v>1.76081681251526</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.75354063510895</v>
+        <v>1.75354027748108</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.81902527809143</v>
+        <v>1.81902539730072</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.88451027870178</v>
+        <v>1.88451015949249</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.85540556907654</v>
+        <v>1.85540568828583</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.84812986850739</v>
+        <v>1.8481297492981</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.86995816230774</v>
+        <v>1.86995804309845</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.8117493391037</v>
+        <v>1.81174921989441</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.85540556907654</v>
+        <v>1.85540568828583</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.89178621768951</v>
+        <v>1.89178609848022</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.90633845329285</v>
+        <v>1.90633869171143</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.90633845329285</v>
+        <v>1.90633869171143</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.89178621768951</v>
+        <v>1.89178609848022</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.84085357189178</v>
+        <v>1.84085369110107</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.8117493391037</v>
+        <v>1.81174921989441</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.8117493391037</v>
+        <v>1.81174921989441</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.8117493391037</v>
+        <v>1.81174921989441</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.74626433849335</v>
+        <v>1.74626445770264</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.77536880970001</v>
+        <v>1.77536904811859</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.9281667470932</v>
+        <v>1.92816710472107</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.97909951210022</v>
+        <v>1.9790997505188</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.99365174770355</v>
+        <v>1.99365198612213</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.03730845451355</v>
+        <v>2.03730869293213</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.10279321670532</v>
+        <v>2.1027934551239</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.03730845451355</v>
+        <v>2.03730869293213</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.99365174770355</v>
+        <v>1.99365198612213</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.99365174770355</v>
+        <v>1.99365198612213</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.97909951210022</v>
+        <v>1.9790997505188</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.95727145671844</v>
+        <v>1.95727121829987</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.91361474990845</v>
+        <v>1.91361486911774</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.86995816230774</v>
+        <v>1.86995804309845</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.84812986850739</v>
+        <v>1.8481297492981</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.03003239631653</v>
+        <v>2.03003215789795</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.00820422172546</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.00820422172546</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.03003239631653</v>
+        <v>2.03003215789795</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.99365174770355</v>
+        <v>1.99365198612213</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.00820422172546</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.03730845451355</v>
+        <v>2.03730869293213</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.03003239631653</v>
+        <v>2.03003215789795</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.03003239631653</v>
+        <v>2.03003215789795</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.05186080932617</v>
+        <v>2.05186057090759</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.02275633811951</v>
+        <v>2.02275609970093</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.99365174770355</v>
+        <v>1.99365198612213</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.00820422172546</v>
+        <v>2.00820398330688</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.96454727649689</v>
+        <v>1.96454739570618</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.97182333469391</v>
+        <v>1.97182369232178</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.97182333469391</v>
+        <v>1.97182369232178</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.94999504089355</v>
+        <v>1.94999539852142</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.9281667470932</v>
+        <v>1.92816710472107</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.98637580871582</v>
+        <v>1.98637568950653</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.07993626594543</v>
+        <v>2.07993602752686</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.07993626594543</v>
+        <v>2.07993602752686</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.08739113807678</v>
+        <v>2.08739137649536</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.08739113807678</v>
+        <v>2.08739137649536</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.24394536018372</v>
+        <v>2.24394559860229</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.4526846408844</v>
+        <v>2.45268440246582</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1363" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.37067985534668</v>
+        <v>2.37068009376526</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>2.33340501785278</v>
+        <v>2.33340525627136</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.31104016304016</v>
+        <v>2.31104040145874</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1376" t="n">
-        <v>2.653968334198</v>
+        <v>2.65396857261658</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.67633366584778</v>
+        <v>2.6763334274292</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1378" t="n">
-        <v>2.67633366584778</v>
+        <v>2.6763334274292</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.44522953033447</v>
+        <v>2.44522976875305</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.34831547737122</v>
+        <v>2.34831523895264</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.36322498321533</v>
+        <v>2.36322474479675</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.33340501785278</v>
+        <v>2.33340525627136</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.31104016304016</v>
+        <v>2.31104040145874</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.33340501785278</v>
+        <v>2.33340525627136</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.31104016304016</v>
+        <v>2.31104040145874</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.40049958229065</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.34831547737122</v>
+        <v>2.34831523895264</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1405" t="n">
-        <v>2.34831547737122</v>
+        <v>2.34831523895264</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.37067985534668</v>
+        <v>2.37068009376526</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>2.40049958229065</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1412" t="n">
-        <v>2.33340501785278</v>
+        <v>2.33340525627136</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.31104016304016</v>
+        <v>2.31104040145874</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.44522953033447</v>
+        <v>2.44522976875305</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.44522953033447</v>
+        <v>2.44522976875305</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.37067985534668</v>
+        <v>2.37068009376526</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.40049958229065</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.37067985534668</v>
+        <v>2.37068009376526</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.37067985534668</v>
+        <v>2.37068009376526</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.40049958229065</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.40049958229065</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.35577011108398</v>
+        <v>2.35576987266541</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.40795469284058</v>
+        <v>2.40795493125916</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.4526846408844</v>
+        <v>2.45268440246582</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.40049958229065</v>
+        <v>2.40049982070923</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.36322498321533</v>
+        <v>2.36322474479675</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.4154098033905</v>
+        <v>2.41540956497192</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.37813496589661</v>
+        <v>2.37813520431519</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.45434880256653</v>
+        <v>2.45434904098511</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.45434880256653</v>
+        <v>2.45434904098511</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.45434880256653</v>
+        <v>2.45434904098511</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.25</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.4695463180542</v>
+        <v>2.46954655647278</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.25</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.4695463180542</v>
+        <v>2.46954655647278</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.25</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.4695463180542</v>
+        <v>2.46954655647278</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.28717947006226</v>
+        <v>2.28717970848083</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.35556697845459</v>
+        <v>2.35556721687317</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.28717947006226</v>
+        <v>2.28717970848083</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.2947781085968</v>
+        <v>2.29477834701538</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.2947781085968</v>
+        <v>2.29477834701538</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.28717947006226</v>
+        <v>2.28717970848083</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.35556697845459</v>
+        <v>2.35556721687317</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.35556697845459</v>
+        <v>2.35556721687317</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.35556697845459</v>
+        <v>2.35556721687317</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.28717947006226</v>
+        <v>2.28717970848083</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.28717947006226</v>
+        <v>2.28717970848083</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.28717947006226</v>
+        <v>2.28717970848083</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.35556697845459</v>
+        <v>2.35556721687317</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.38596177101135</v>
+        <v>2.38596153259277</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.01362991333008</v>
+        <v>2.01363015174866</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.16560196876526</v>
+        <v>2.16560173034668</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.19599652290344</v>
+        <v>2.19599676132202</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.27198266983032</v>
+        <v>2.27198243141174</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.27198266983032</v>
+        <v>2.27198243141174</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.27958130836487</v>
+        <v>2.27958106994629</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.2947781085968</v>
+        <v>2.29477834701538</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.30997538566589</v>
+        <v>2.30997562408447</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.3403697013855</v>
+        <v>2.34036993980408</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -71672,7 +71672,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2743" t="n">
-        <v>163790</v>
+        <v>165295</v>
       </c>
       <c r="C2743" t="n">
         <v>16.5</v>
@@ -71690,6 +71690,32 @@
         <v>16.4400005340576</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>58654</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>16.8600006103516</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>16.3799991607666</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>16.4400005340576</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>16.7600002288818</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>16.7600002288818</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
